--- a/question_banks/testuser1/10th_Kannada_LBA_Question_Bank_2026.xlsx
+++ b/question_banks/testuser1/10th_Kannada_LBA_Question_Bank_2026.xlsx
@@ -1,23 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\qb\question_banks\testuser1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF34044-032F-4A82-9538-ECF4E1CF53B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$231</definedName>
   </definedNames>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="564">
   <si>
     <t>QNo.</t>
   </si>
@@ -790,63 +796,968 @@
     <t>ಸಾಮಾಜಿಕ ಪಿಡುಗುಗಳು. (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
   </si>
   <si>
-    <t>ನಮ್ಮ ಮನೆ</t>
-  </si>
-  <si>
-    <t>ಮುತ್ತು ಒಡೆದರೆ ಹೋಯಿತು ಮಾತು ಆಡಿದರೆ ಹೋಯಿತು</t>
+    <t>ಗದ್ಯಪಾಠ : 6. ಶಬರಿ</t>
+  </si>
+  <si>
+    <t>ಪ್ರಾಣೇಂದ್ರಿಯ' ಪದವು ಈ ಸಂಧಿಗೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) (ಎ) ಗುಣ (ಬಿ) ಸವರ್ಣ (ಸಿ) ಯಣ್ (ಡಿ) ವೃದ್ಧಿ</t>
+  </si>
+  <si>
+    <t>ಸವರ್ಣದೀರ್ಘ ಸಂಧಿಗೆ ಈ ಪದವು ಸೇರಿದೆ (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಎ) ಮಹರ್ಷಿ (ಬಿ) ವಧೂಪೇತ (ಸಿ) ಊರೂರು (ಡಿ) ಕೋಟ್ಯನುಕೋಟಿ</t>
+  </si>
+  <si>
+    <t>ಶರಚ್ಚಂದ್ರ' ಪದವು ಈ ಸಂಧಿಯದ್ದಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2020, 2023 (ಎ) ಶ್ಚುತ್ವ (ಬಿ) ಯಣ್ (ಸಿ) ವೃದ್ಧಿ (ಡಿ) ಜಶ್ತ್ವ</t>
+  </si>
+  <si>
+    <t>ಒಮ್ಮೊಮ್ಮೆ' ಪದದಲ್ಲಿರುವ ಸಂಧಿ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) (ಎ) ಆಗಮಸಂಧಿ (ಬಿ) ಆದೇಶಸಂಧಿ (ಸಿ) ಲೋಪಸಂಧಿ (ಡಿ) ಅನುನಾಸಿಕ</t>
+  </si>
+  <si>
+    <t>ವಾಗ್ದೇವಿ' ಪದದಲ್ಲಿರುವ ಸಂಧಿ (ಸ್ಮರಣೆ- ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2019, 2024. (ಎ) ಅನುನಾಸಿಕ (ಬಿ) ವೃದ್ಧಿ (ಸಿ) ಆದೇಶ (ಡಿ) ಜಶ್ತ್ವ</t>
+  </si>
+  <si>
+    <t>ಉನ್ಮಾದ' ಪದವು ಈ ಸಂಧಿಗೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) (ಎ) ಸವರ್ಣದೀರ್ಘ (ಬಿ) ಗುಣ (ಸಿ) ಅನುನಾಸಿಕ (ಡಿ) ಜಶ್ತ್ವ</t>
+  </si>
+  <si>
+    <t>ಸೂರ್ಯೋದಯ' ಪದವು ಈ ಸಂಧಿಗೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸುಲಭ) ಸೆಪ್ಟೆಂಬರ್ 2020. (ಎ) ಸವರ್ಣದೀರ್ಘ (ಬಿ) ವೃದ್ಧಿ (ಸಿ) ಗುಣ (ಡಿ) ಯಣ್</t>
+  </si>
+  <si>
+    <t>ಮಾತಂತು' ಪದವು ಈ ಸಂಧಿಗೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2021. (ಎ) ಅನುನಾಸಿಕ (ಬಿ) ಲೋಪ (ಸಿ) ವೃದ್ಧಿ (ಡಿ) ಯಣ್</t>
+  </si>
+  <si>
+    <t>ಮಳೆಗಾಲ' ಪದವು ಈ ಸಂಧಿಗೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2022. (ಎ) ಲೋಪ (ಬಿ) ಆಗಮ (ಸಿ) ಆದೇಶ (ಡಿ) ಗುಣ</t>
+  </si>
+  <si>
+    <t>ದಿಗಂತ' ಪದವು ಈ ಸಂಧಿಗೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2023, ಜೂನ್ 2022. (ಎ) ಗುಣ (ಬಿ) ಜಶ್ತ್ವ (ಸಿ) ವೃದ್ಧಿ (ಡಿ) ಶ್ಚುತ್ವ</t>
+  </si>
+  <si>
+    <t>ದೇವೇಂದ್ರ' ಪದವು ಈ ಸಂಧಿಗೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಜೂನ್ 2023, ಮೇ-2025. (ಎ) ಲೋಪ (ಬಿ) ಆಗಮ (ಸಿ) ಗುಣ (ಡಿ) ಆದೇಶ</t>
+  </si>
+  <si>
+    <t>ಮಹರ್ಷಿ' ಪದವು ಈ ಸಂಧಿಗೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಜೂನ್ 2018. (ಎ) ಆದೇಶ (ಬಿ) ಗುಣ (ಸಿ) ಸವರ್ಣದೀರ್ಘ (ಡಿ) ಯಣ್</t>
+  </si>
+  <si>
+    <t>ಮದೋನ್ಮತ್ತ' ಪದವು ಈ ಸಂಧಿಗೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2024. (ಎ) ಲೋಪ (ಬಿ) ಆದೇಶ (ಸಿ) ಆಗಮ (ಡಿ) ಗುಣ</t>
+  </si>
+  <si>
+    <t>ಅನುನಾಸಿಕ ಸಂಧಿಗೆ ಉದಾಹರಣೆಯಿದು (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಆಗಸ್ಟ್ 2024. (ಎ) ದೇವೇಂದ್ರ (ಬಿ) ಮಳೆಗಾಲ (ಸಿ) ವಾಙ್ಮಯ (ಡಿ) ದಿಗಂತ</t>
+  </si>
+  <si>
+    <t>ಅನುನಾಸಿಕ ಸಂಧಿಗೆ ಉದಾಹರಣೆಯಾಗಿರುವ ಪದ (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಜೂನ್ 2024. (ಎ) ಮಹಾತ್ಮ (ಬಿ) ವಿದ್ಯಾಭ್ಯಾಸ (ಸಿ) ಅತ್ಯಾದರ (ಡಿ) ಸನ್ಮಾನ</t>
+  </si>
+  <si>
+    <t>ಕೆಳಗಿನವುಗಳಲ್ಲಿ ಮೊದಲೆರಡು ಪದಗಳಿಗಿರುವ ಸಂಬಂಧದಂತೆ ಮೂರನೆಯ ಪದಕ್ಕೆ ಸರಿಹೊಂದುವ ಸಂಬಂಧೀ ಪದವನ್ನು ಬರೆಯಿರಿ :</t>
+  </si>
+  <si>
+    <t>ಭೇದವಿಲ್ಲ : ಆಗಮಸಂಧಿ : : ಕಡುವೆಳ್ದು : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2026.</t>
+  </si>
+  <si>
+    <t>ಬುದ್ಧಿಯೊಡೆಯ : ಆಗಮಸಂಧಿ : : ಏಕೈಕ : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ಅಷ್ಟೈಶ್ವರ್ಯ : ವೃದ್ಧಿಸಂಧಿ : : ಅತ್ಯವಸರ : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ಶರಚ್ಚಂದ್ರ : ಶ್ಚುತ್ವಸಂಧಿ : : ಸಂಗ್ರಹಾಲಯ : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಜೂನ್ 2018.</t>
+  </si>
+  <si>
+    <t>ನಿಜಾಶ್ರಮ : ಸವರ್ಣದೀರ್ಘಸಂಧಿ : : ವೇದಿಯಲ್ಲಿ : (ಗ್ರಹಿಕೆ - ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ಭೂಮಿಜಾತೆ ಎಂದರೆ ಯಾರು? (ಸ್ಮರಣೆ-ಸುಲಭ)</t>
+  </si>
+  <si>
+    <t>ಶ್ರೀರಾಮನ ತಂದೆಯ ಹೆಸರೇನು? (ಸ್ಮರಣೆ-ಸುಲಭ)</t>
+  </si>
+  <si>
+    <t>ಸೌಮಿತ್ರಿ ಎಂದರೆ ಯಾರು? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ಶಬರಿಯು ಯಾರ ಆಶ್ರಮದಲ್ಲಿ ವಾಸವಿದ್ದಳು? (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2019, ಜೂನ್ 2019.</t>
+  </si>
+  <si>
+    <t>ರಾಮ ಲಕ್ಷ್ಮಣರಿಗೆ ಮತಂಗಾಶ್ರಮಕ್ಕೆ ಹೋಗಲು ಸೂಚಿಸಿದವರು ಯಾರು? (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2017, 2018.</t>
+  </si>
+  <si>
+    <t>ಶ್ರೀರಾಮನಿಗೆ ಸಮರ್ಪಿಸಲು ಶಬರಿ ಏನನ್ನು ಸಂಗ್ರಹಿಸಿದ್ದಳು? (ಸ್ಮರಣೆ-ಸುಲಭ)</t>
+  </si>
+  <si>
+    <t>ರಾಮನ ಬರುವಿಕೆಗಾಗಿ ಮತಂಗಾಶ್ರಮದಲ್ಲಿ ಕಾಯುತ್ತಿದ್ದವರು ಯಾರು? (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2020.</t>
+  </si>
+  <si>
+    <t>ರಾಮನು ಗಿರಿವನವನ್ನು ಪ್ರಾರ್ಥಿಸಿದ ಬಗೆಯನ್ನು ಬರೆಯಿರಿ. (ಗ್ರಹಿಕೆ-ಸುಲಭ) (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಲಕ್ಷ್ಮಣನು ಅಣ್ಣನನ್ನು ಹೇಗೆ ಸಂತೈಸಿದನು? (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಜೂನ್ 2024, ಆಗಸ್ಟ್ 2024. (ಕ.ಫ-3)</t>
+  </si>
+  <si>
+    <t>ರಾಮನ ಸ್ವಾಗತಕ್ಕಾಗಿ ಶಬರಿ ಮಾಡಿಕೊಂಡಿದ್ದ ಸಿದ್ಧತೆಗಳಾವುವು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಶಬರಿಯು ರಾಮಲಕ್ಷ್ಮಣರನ್ನು ಉಪಚರಿಸಿದ ರೀತಿಯನ್ನು ವಿವರಿಸಿ. (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2020, 2025, ಜೂನ್ 2023. (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಆತಿಥ್ಯ ಸ್ವೀಕರಿಸಿದ ರಾಮಲಕ್ಷ್ಮಣರು ಶಬರಿಗೆ ಹೇಳಿದ ಮಾತುಗಳಾವುವು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಶಬರಿಯು ಶ್ರೀರಾಮನ ಗುಣಗಾನವನ್ನು ಮಾಡಿದ ರೀತಿ ತಿಳಿಸಿ. (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಶಬರಿಯು ರಾಮನಿಗಾಗಿ ತಂದಿದ್ದ ಹೂವು, ಹಣ್ಣು, ತಳಿರುಗಳನ್ನು ಉದ್ದೇಶಿಸಿ ಹಾಡಿದ ಬಗೆಯನ್ನು ಬರೆಯಿರಿ. (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಪು. ತಿ. ನರಸಿಂಹಾಚಾರ್ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2017, 2018, ಜೂನ್ 2019, 2023, 2024, ಸೆಪ್ಟೆಂಬರ್ 2020.</t>
+  </si>
+  <si>
+    <t>ತಾಳಿದವನು ಬಾಳಿಯಾನು. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2026.</t>
+  </si>
+  <si>
+    <t>“ಆವುದೀ ಮರುಳು? ನಮ್ಮೆಡೆಗೆ ಬರುತಿಹುದು." (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>“ನಾಚುತಿಹೆನೀ ಪೂಜೆಯೀ ನಲುಮೆಯಿಂದ." (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>“ತಾಯಿ, ದಾರಿಗರಿಗೆ ಬೀಡಿಲ್ಲಿ ದೊರೆಯುವುದೇ?” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>"ರೂಪಿನಂತೆ ಮಾತು ಕೂಡ ಎನಿತುದಾರವಾಗಿದೆ?” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>“ಬೆಳಕಿಗೊಲಿದವರ್ ಉರಿವ ಬತ್ತಿಯ ಕರುಕ ಕಾಣರು.” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ) ಮಾರ್ಚ್ 2015, 2019.</t>
+  </si>
+  <si>
+    <t>“ರಾಮನೇ ಧೈರ್ಯಗೆಡೆ ಸ್ಥೈರ್ಯಕೆಡೆ ಯಾರು?” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>“ಅಯ್ಯೋ ಏನೂ ಅಣಿಯೆ ಇಲ್ಲ” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>“ನಿನ್ನಾದರದೊಳು ಸುಖಿ ನಾವು" (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>“ಇಂಥ ಶಿಷ್ಯೆಯಂ ಪಡೆದ ನಿನ್ನ ಗುರುಗಳೆಂಥರೋ" (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>"ಮನ ಒಪ್ಪಿದರೂ ಎದೆಯೊಪ್ಪದಲಾ!” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ಶಬರಿಯ ಚಿಂತೆ ಹಿಂಗಿಹೋದ ಸಂದರ್ಭದ ಸ್ವಾರಸ್ಯವನ್ನು ವಿವರಿಸಿ. / ಶ್ರೀರಾಮನ ಆಗಮನದಿಂದ ಶಬರಿಯ ಚಿಂತೆ ತೀರಿಹೋದ ಸಂದರ್ಭವನ್ನು ವಿವರಿಸಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2026, ಜೂನ್ 2017. (ಕ.ಫ-3)</t>
+  </si>
+  <si>
+    <t>ಶಬರಿಯ ಸಡಗರ, ಸಂತೋಷ ಮೇಳದವರ ಹಾಡಿನಲ್ಲಿ ಹೇಗೆ ವರ್ಣಿತವಾಗಿದೆ? ತಿಳಿಸಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಜೂನ್ 2017, 2018. (ಕ.ಫ-3)</t>
+  </si>
+  <si>
+    <t>ನಂಬಿ ಕೆಟ್ಟವರಿಲ್ಲ' ಎಂಬ ಮಾತು ಶಬರಿಯ ಪಾಲಿಗೆ ಹೇಗೆ ನಿಜವಾಗಿದೆ. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಜೂನ್ 2018. (ಕ.ಫ-3)</t>
+  </si>
+  <si>
+    <t>ಶಬರಿ ಗದ್ಯಪಾಠದಲ್ಲಿ ಬರುವ ರಾಮ ಮತ್ತು ಶಬರಿಯ ನಡುವಿನ ಸಂಭಾಷಣೆಯನ್ನು ಆಂಗ್ಲ ಭಾಷೆಯಲ್ಲಿ ಬರೆದು ಅಭಿನಯಿಸಿರಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) (ಕ.ಫ.-14)</t>
+  </si>
+  <si>
+    <t>ಒಳ್ಳೆಯ ಪುಸ್ತಕಗಳು ಶಿಕ್ಷಕರಿಗಿಂತ ಉತ್ತಮ ಮಾರ್ಗದರ್ಶನವನ್ನು ನೀಡಬಲ್ಲವು ಎಂದು ತಜ್ಞರೊಬ್ಬರು ಅಭಿಪ್ರಾಯಪಡುತ್ತಾರೆ. ಪುಸ್ತಕಗಳನ್ನು ಓದುವುದರಿಂದ ಅನುಭವ ಹೆಚ್ಚುತ್ತದೆ. ವ್ಯಕ್ತಿತ್ವ ಪರಿಪಕ್ವಗೊಳ್ಳುತ್ತೆ. ಹೇಗೆ ಓದಬೇಕು ಎಂಬುದರ ಬಗ್ಗೆ ಈಗಾಗಲೇ ಸಾಕಷ್ಟು ಸಂಶೋಧನೆಗಳು ನಡೆದಿವೆ. ಮನೋವಿಜ್ಞಾನಿಗಳು ಹಾಗೂ ಶಿಕ್ಷಣ ತಜ್ಞರ ಪ್ರಕಾರ "ಓದಲು ದೃಢವಾದ ಸಂಕಲ್ಪವಿರಬೇಕು. ಕಲಿಯಬೇಕೆನ್ನುವ ಹಂಬಲ ಮತ್ತು ಕಲಿಯುವೆ ಎಂಬ ಆತ್ಮವಿಶ್ವಾಸ ಹುಟ್ಟದಿದ್ದರೆ ಓದಿನಲ್ಲಿ ಅಭಿರುಚಿ ಹುಟ್ಟುವುದಿಲ್ಲ. 'ಎಷ್ಟು ಓದಿದರು ನೆನಪಲ್ಲೇ ಉಳಿಯುವುದಿಲ್ಲ' ಎಂದು ಹಳಿಯುತ್ತ ಪುಸ್ತಕವನ್ನು ದೂರ ಎಸೆಯುವ ಬದಲಾಗಿ ಮತ್ತೆ ಮತ್ತೆ ಓದಿ ಸ್ಮರಣಶಕ್ತಿಯನ್ನು ಉದ್ದೀಪನಗೊಳಿಸಿಕೊಳ್ಳಲು ಪ್ರಯತ್ನಿಸಬೇಕು”. ಓದಿನ ಮುಖ್ಯ ಉದ್ದೇಶ ಅರ್ಥಮಾಡಿಕೊಳ್ಳುವುದು. ಪರೀಕ್ಷೆಯಲ್ಲಿ ಪಾಸಾಗುವ ಉದ್ದೇಶದಿಂದ ಕಾಟಾಚಾರಕ್ಕೆ ಓದಿದ ಯಾವ ಅಂಶವೂ ನಿಮ್ಮ ಮನಸ್ಸಿನಲ್ಲಿ ಉಳಿಯದು. ಈ ಅರ್ಥವ್ಯಾಪ್ತಿಯಲ್ಲಿ ಓದು ಅಧ್ಯಯನ ಮಟ್ಟಕ್ಕೇರುವುದು. ನಿಮ್ಮ ಅಧ್ಯಯನ ಅಥವಾ ಓದು ಸಫಲವಾಗಿದೆಯೇ ಎಂಬುದನ್ನು ನೀವೇ ಪರೀಕ್ಷಿಸಿಕೊಳ್ಳಬಹುದು. ಓದಿದ ತರುವಾಯ ಪುಸ್ತಕವನ್ನು ಮುಚ್ಚಿಟ್ಟು ಓದಿದ್ದನ್ನು ಮತ್ತೆ ನೆನಪು ಮಾಡಿಕೊಳ್ಳಬೇಕು. ಕೇವಲ ಓದಿದರೆ ಪ್ರಯೋಜನವಿಲ್ಲ. ಓದಿದ್ದನ್ನು ಮನನ ಮಾಡಿಕೊಂಡರೆ ಮಾತ್ರ ಹೆಚ್ಚು ಪ್ರಯೋಜನವಾಗುತ್ತದೆ ಎಂಬುದನ್ನು ಅರ್ಥೈಸಿಕೊಂಡು ಓದಿನ ಸಫಲತೆಯನ್ನು ಪರೀಕ್ಷಿಸಿಕೊಳ್ಳಬಹುದು. ಪ್ರಶ್ನೆಗಳು : ಅ. ನಮ್ಮ ಓದಿನ ಸಫಲತೆಯನ್ನು ಪರೀಕ್ಷಿಸುವುದು ಹೇಗೆ? ಆ. ನಮ್ಮ ಓದು ಹೇಗಿರಬೇಕು?</t>
+  </si>
+  <si>
+    <t>ನಿಮ್ಮನ್ನು ಬೆಂಗಳೂರಿನ ರಾಜಾಜಿನಗರದ 'ಅನನ್ಯಾ' ಎಂದು ಭಾವಿಸಿಕೊಂಡು ನಿಮ್ಮ ಬಡಾವಣೆಗೆ ಶುದ್ಧ ಕುಡಿಯುವ ನೀರಿನ ಘಟಕವನ್ನು ಮಂಜೂರು ಮಾಡುವಂತೆ ಕೋರಿ ಬೆಂಗಳೂರಿನ ಮಹಾನಗರಪಾಲಿಕೆಯ ಮೇಯರ್‌ಗೆ ಪತ್ರವನ್ನು ಬರೆಯಿರಿ.</t>
+  </si>
+  <si>
+    <t>ಗ್ರಂಥಾಲಯಗಳ ಮಹತ್ತ್ವ. (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ಗದ್ಯಪಾಠ : 7. ಲಂಡನ್ ನಗರ</t>
+  </si>
+  <si>
+    <t>ಜುಳುಜುಳು' ಇಲ್ಲಿರುವ ವ್ಯಾಕರಣಾಂಶ (ಸ್ಮರಣೆ-ಸುಲಭ) (ಎ) ಜೋಡುನುಡಿ (ಬಿ) ಅನುಕರಣಾವ್ಯಯ (ಸಿ) ದ್ವಿರುಕ್ತಿ (ಡಿ) ಅವ್ಯಯ</t>
+  </si>
+  <si>
+    <t>ಮನೆಮಠ' ಇಲ್ಲಿರುವ ವ್ಯಾಕರಣಾಂಶ (ಸ್ಮರಣೆ-ಸುಲಭ) (ಎ) ಅನುಕರಣಾವ್ಯಯ (ಬಿ) ಜೋಡುನುಡಿ (ಸಿ) ದ್ವಿರುಕ್ತಿ (ಡಿ) ಅವ್ಯಯ</t>
+  </si>
+  <si>
+    <t>ಮೊಟ್ಟಮೊದಲು' ಪದವು ಈ ವ್ಯಾಕರಣಾಂಶಕ್ಕೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2019. (ಎ) ಅವ್ಯಯ (ಬಿ) ಜೋಡುನುಡಿ (ಸಿ) ಅನುಕರಣಾವ್ಯಯ (ಡಿ) ದ್ವಿರುಕ್ತಿ</t>
+  </si>
+  <si>
+    <t>ಕೆನೆಮೊಸರು' ಇಲ್ಲಿರುವ ವ್ಯಾಕರಣಾಂಶ (ಸ್ಮರಣೆ-ಸುಲಭ) ಜೂನ್ 2018. (ಎ) ಜೋಡುನುಡಿ (ಬಿ) ಅನುಕರಣಾವ್ಯಯ (ಸಿ) ದ್ವಿರುಕ್ತಿ (ಡಿ) ಅವ್ಯಯ</t>
+  </si>
+  <si>
+    <t>ಬಟ್ಟಬಯಲು' ಪದವು ಈ ವ್ಯಾಕರಣಾಂಶಕ್ಕೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ-ಸುಲಭ) ಜೂನ್ 2018. (ಎ) ಅನುಕರಣಾವ್ಯಯ (ಬಿ) ಜೋಡುನುಡಿ (ಸಿ) ದ್ವಿರುಕ್ತಿ (ಡಿ) ಅವ್ಯಯ</t>
+  </si>
+  <si>
+    <t>ಓಡುಓಡು : ದ್ವಿರುಕ್ತಿ : : ಧೀರಶೂರ : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಜೂನ್ 2024.</t>
+  </si>
+  <si>
+    <t>ಕಟ್ಟಕಡೆಗೆ : ಕಡೆಗೆಕಡೆಗೆ : : ಬಟ್ಟಬಯಲು : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2018.</t>
+  </si>
+  <si>
+    <t>ಕೆನೆಮೊಸರು : ಜೋಡುನುಡಿ : : ಗರಿಗರಿ : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಸೆಪ್ಟೆಂಬರ್ 2020.</t>
+  </si>
+  <si>
+    <t>ಮಕ್ಕಳುಮರಿ : ಜೋಡುನುಡಿ : : ಓಡಿಓಡಿ : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2022.</t>
+  </si>
+  <si>
+    <t>ಬಟ್ಟಬಯಲು : ದ್ವಿರುಕ್ತಿ : : ಹುಳಹುಪ್ಪಡಿ : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಜೂನ್ 2022, 2023.</t>
+  </si>
+  <si>
+    <t>ಹಣ್ಣುಹಂಪಲು : ಜೋಡುನುಡಿ : : ಬೇಡಬೇಡ : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಮಾ-2023.</t>
+  </si>
+  <si>
+    <t>ಕೆನೆಮೊಸರು : ಜೋಡುನುಡಿ : : ಸಾಕುಸಾಕು : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2024.</t>
+  </si>
+  <si>
+    <t>ಹುಳಹುಪ್ಪಡಿ : ಜೋಡುನುಡಿ : : ತುತ್ತತುದಿ : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಆಗಸ್ಟ್ 2024.</t>
+  </si>
+  <si>
+    <t>ತುತ್ತತುದಿ : ದ್ವಿರುಕ್ತಿ : : ಹಾಲوجೇನು : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಜೂನ್ 2019, ಮೇ 2025.</t>
+  </si>
+  <si>
+    <t>ಸತಿಪತಿ : ಜೋಡುನುಡಿ : : ದೊಡ್ಡದೊಡ್ಡ : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2019, 2025.</t>
+  </si>
+  <si>
+    <t>ಲಂಡನ್ನಿನ ರಸ್ತೆಗಳಲ್ಲಿ ನಿಲ್ಲುವುದನ್ನು ತಪ್ಪಿಸಲು ಮಾಡಿರುವ ವ್ಯವಸ್ಥೆಯೇನು? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ಲೇಖಕರು ವರ್ಣಿಸಿದ ಲಂಡನ್ನಿನ ಪೇಟೆಯಲ್ಲಿರುವ ಸ್ಟೇಷನರಿ ಅಂಗಡಿಯ ಹೆಸರೇನು? (ಸ್ಮರಣೆ-ಸುಲಭ) ಆಗಸ್ಟ್ 2024.</t>
+  </si>
+  <si>
+    <t>ಲಂಡನ್ ನಗರದಲ್ಲಿ ಪ್ರಸಿದ್ಧಿ ಪಡೆದ ಸಿಂಪಿಗಳು ಯಾರು? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಲಂಡನ್ ನಗರದಲ್ಲಿ ನೆಲ್ಸನ್‌ರವರ ಮೂರ್ತಿಯಿರುವ ಸ್ಥಳದ ಹೆಸರೇನು? (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2019, ಜೂನ್ 2018.</t>
+  </si>
+  <si>
+    <t>ವೆಸ್ಟ್ ಮಿನ್‌ಸ್ಟರ್ ಅಬೆ' ಯಾರ ಸ್ಮಾರಕವಾಗಿದೆ? (ಸ್ಮರಣೆ-ಸುಲಭ) ಜೂನ್ 2019.</t>
+  </si>
+  <si>
+    <t>ಆಂಗ್ಲ ಸಾಮ್ರಾಜ್ಯದ ವೈಭವ ಕಂಡುಬರುವ ಓಣಿ ಯಾವುದು? (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2024, 2026, ಜೂನ್ 2022, 2023, 2024.</t>
+  </si>
+  <si>
+    <t>೩ನೇ ಎಡ್ವರ್ಡನು ತಂದ ಶಿಲೆಗೆ ಇರುವ ಹೆಸರೇನು? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>೩ನೇ ಎಡ್ವರ್ಡನು ಯಾವ ಅರಸರಿಂದ 'ಸ್ಟೋನ್ ಆಫ್ ಸ್ಕೋನ್' ಎಂಬ ಶಿಲೆಯನ್ನು ಕಿತ್ತುಕೊಂಡು ತಂದಿದ್ದನು? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ಪ್ರವಾಸವನ್ನು ಕುರಿತು ಬೇಕನ್ನನು ಹೇಳಿದ ಮಾತು ಯಾವುದು? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ಮನೆ ಹಿಡಿದು ಇರುವ ತರುಣನ ಬುದ್ಧಿ ಮನೆಯ ಮಟ್ಟದ್ದೇ' ಎಂದ ಆಂಗ್ಲ ಕವಿ ಯಾರು? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ವೂಲವರ್ಥ ಅಂಗಡಿಯಲ್ಲಿ ಸಿಗುವ ವಸ್ತುಗಳಾವುವು? (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2026, ಜೂನ್ 2019. (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಲಂಡನ್ನಿನ ಹೆಣ್ಣು ಮಕ್ಕಳು ಯಾವ ಯಾವ ಕೆಲಸದಲ್ಲಿ ನಿಯುಕ್ತರಾಗಿರುತ್ತಾರೆ? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2022, ಸೆಪ್ಟೆಂಬರ್ 2020. (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಟೊಪ್ಪಿಗೆಯ ವಿಶೇಷತೆಯನ್ನು ಲೇಖಕರು ಹೇಗೆ ದಾಖಲಿಸಿದ್ದಾರೆ? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾ-2022, 2024. (ಕ.ಫ-3)</t>
+  </si>
+  <si>
+    <t>ಪೊಯೆಟ್ಸ್ ಕಾರ್ನರ್‌ನಲ್ಲಿ ಯಾವ ಯಾವ ಕವಿಗಳ ಸಮಾಧಿಗಳಿವೆ? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಸಾಮ್ರಾಟರ ರಾಜ್ಯಾಭಿಷೇಕವಾಗುವ ಸಿಂಹಾಸನದ ಮೇಲಿರುವ ಕಲ್ಲುಪಾಟಿಯ ವಿಶೇಷತೆಯೇನು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಜೂನ್ 2019, 2016, 2022, ಸೆಪ್ಟೆಂಬರ್ 2020. (ಕ.ಫ-3)</t>
+  </si>
+  <si>
+    <t>ಲಂಡನ್ ನಗರದಲ್ಲಿರುವ ಇಂಡಿಯಾ ಆಫೀಸ್‌ನ್ನು ಕುರಿತು ತಿಳಿಸಿ. (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಲಂಡನ್ ನಗರದ ವೆಸ್ಟ್ ಮಿನ್‌ಸ್ಟರ್ ಅಬೆ ಮಂದಿರದಲ್ಲಿನ ರಾಜವಿಭಾಗದ ಕುರಿತು ಬರೆಯಿರಿ. (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ವಿ. ಕೃ. ಗೋಕಾಕ್ (ಸ್ಮರಣೆ-ಸುಲಭ) ಜೂನ್ 2017.</t>
+  </si>
+  <si>
+    <t>“ವೂಲವರ್ಥ ಸ್ಟೇಷನರಿ ಅಂಗಡಿ ಪ್ರಾಚೀನ ಮಹಾಕಾವ್ಯದಂತೆ ಮಹಾಕೋಶವಾಗಿದೆ." (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ದೇಶ ಸುತ್ತು ; ಕೋಶ ಓದು. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2019, ಜೂನ್ 2018.</t>
+  </si>
+  <si>
+    <t>“ನಿಮ್ಮ ದೇಶದ ಗೌರವವನ್ನು ಕಾಯಿರಿ! ಇದು ದೊಡ್ಡದಾದ ರಾಷ್ಟ್ರ” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2023.</t>
+  </si>
+  <si>
+    <t>"ಹೊತ್ತು! ಹೊತ್ತು! ಹೊತ್ತೇ ಹಣ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2024, ಆಗಸ್ಟ್ 2024.</t>
+  </si>
+  <si>
+    <t>"ಯಾರನ್ನು ತುಳಿದರೇನು! ಎಲ್ಲಿ ಹೆಜ್ಜೆ ಹಾಕಿದರೇನು? ಎಲ್ಲವೂ ಅಷ್ಟೆ! ಮಣ್ಣು! ಮಣ್ಣು!” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>"ಪ್ರವಾಸವು ಶಿಕ್ಷಣದ ಒಂದು ಭಾಗವಾಗಿದೆ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2018, 2025, ಜೂನ್ 2023.</t>
+  </si>
+  <si>
+    <t>“ಗಾಡಿಗಳು ದಢದಢ ಹೋಗುತ್ತಿರುತ್ತವೆ! ವಿಚಿತ್ರ ಸೃಷ್ಟಿ!" (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>“ಈ ದೊಡ್ಡ ಬೀದಿಯು ಸಾಮ್ರಾಜ್ಯದ ಬೀದಿ” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>“ಹೆಜ್ಜೆ ಹೆಜ್ಜೆಗೆ ಇತಿಹಾಸದ ಅಡಿಗಲ್ಲುಗಳು ದೊರೆಯುತ್ತವೆ" (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>"ಮನುಷ್ಯನಂತೆ ಟೊಪ್ಪಿಗೆಯಲ್ಲವೆ? ಒಬ್ಬ ಮನುಷ್ಯಳಂತೆ ಇನ್ನೊಬ್ಬಳಿಲ್ಲ" (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>“ಅಡಿಗಡಿಗೆ ಇತಿಹಾಸವನ್ನು ದಾಟುತ್ತೇವೆ! ಎಂಥ ವಿಚಿತ್ರ!” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>“ಮನೆ ಹಿಡಿದು ಇರುವ ತರುಣನ ಬುದ್ಧಿ ಮನೆಯ ಮಟ್ಟ" (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ) ಮಾರ್ಚ್ 2024, ಜೂನ್ 2024.</t>
+  </si>
+  <si>
+    <t>"ಪಟ್ಟಾಭಿಷೇಕವಾಗುವಾಗ ಮಾತ್ರ ಸಾಮ್ರಾಟರು ಇದರ ಮೇಲೆ ಕೂಡಬೇಕು” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ) ಮೇ 2025.</t>
+  </si>
+  <si>
+    <t>"ಸಿನಿಮಾ ಗೃಹದಲ್ಲಿ ನಿಮ್ಮ ಜಾಗವನ್ನು ಹುಡುಕಿ ಕೊಡುವವರು ಹೆಣ್ಣು"</t>
+  </si>
+  <si>
+    <t>ಲಂಡನ್ ನಗರ ವೀಕ್ಷಣೆಯಲ್ಲಿ ಲೇಖಕರು ಗುರುತಿಸಿರುವ ವಿಶೇಷತೆಗಳನ್ನು ಸಂಗ್ರಹಿಸಿ ಬರೆಯಿರಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ವೆಸ್ಟ್ ಮಿನ್‌ಸ್ಟರ್ ಅಬೆ' ಪ್ರಾರ್ಥನಾ ಮಂದಿರ ಒಂದು ವಿಶೇಷ ಸ್ಮಾರಕ ಎಂಬುದನ್ನು ವಿವರಿಸಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>`ವೆಸ್ಟ್ ಮಿನ್‌ಸ್ಟರ್ ಅಬೆ' ಪ್ರಾರ್ಥನಾ ಮಂದಿರದಲ್ಲಿನ ರಾಯಲ್ ಚಾಪೆಲ್ ಮತ್ತು ಸ್ಟೋನ್ ಆಫ್ ಸ್ಕೋನ್ ಗಳ ವಿಶೇಷತೆಯನ್ನು ಕುರಿತು ಬರೆಯಿರಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ) ಮಾರ್ಚ್ 2020.</t>
+  </si>
+  <si>
+    <t>ವೂಲವರ್ಥ ಸ್ಟೇಷನರಿ ಅಂಗಡಿ ಹಾಗೂ ಲಂಡನ್ನಿನಲ್ಲಿ ಹೆಣ್ಣನ್ನು ಸತ್ಕರಿಸುವ ರೀತಿಯನ್ನು ಲೇಖಕರು ಹೇಗೆ ವಿವರಿಸಿದ್ದಾರೆ. (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ) ಮಾರ್ಚ್ 2020.</t>
+  </si>
+  <si>
+    <t>ಅಯ್ಯೋ! ನನಗೆ ವೇಳೆ ಸಾಲದು ಎಂದು ಕೊರಗುವವರು ಬಹಳ ಮಂದಿ ಇದ್ದಾರೆ. ವೇಳೆ ಎನ್ನುವುದು ಬಂಡವಾಳ ಹೂಡಿಕೆಯಿದ್ದಂತೆ. ಯಾರು ಇರುವ ಸಮಯವನ್ನು ಸರಿಯಾಗಿ, ಸಮರ್ಪಕವಾಗಿ ನಿರ್ವಹಿಸಬಲ್ಲರೋ ಅವರು ಜೀವನವನ್ನು ಚೆನ್ನಾಗಿ ನಿರ್ವಹಿಸಬಲ್ಲರು. 'ಹೊತ್ತೇ ಮುತ್ತು' ಅಲ್ಲವೇ? ಸಮಯ ಪ್ರಜ್ಞೆ ಇರುವವರಿಗೆ ಯಶಸ್ಸು ಕಟ್ಟಿಟ್ಟ ಬುತ್ತಿ. ಯಾರಲ್ಲಿ ಜೀವನದ ಬಗ್ಗೆ ಸ್ಪಷ್ಟವಾದ ಗುರಿಯಿರುವುದಿಲ್ಲವೋ ಅಂತಹವರು ಸಮಯವನ್ನು ಬೇಕಾಬಿಟ್ಟಿಯಾಗಿ ಪೋಲು ಮಾಡುತ್ತಿರುತ್ತಾರೆ. ವಿದ್ಯಾರ್ಥಿಗಳು ಜೀವನದಲ್ಲಿ ಧೈಯಗಳನ್ನು ಹೊಂದುವುದರ ಜೊತೆಗೆ ಯಾವ ಕೆಲಸಕ್ಕೆ ಆದ್ಯತೆ ನೀಡಬೇಕು ಎಂಬ ವಿವೇಕವನ್ನು ಹೊಂದಿರಬೇಕು. ಟಿ.ವಿ.ಯಲ್ಲಿ ಎಷ್ಟೇ ಒಳ್ಳೆಯ ಕಾರ್ಯಕ್ರಮಗಳು ಪ್ರಸಾರವಾಗುತ್ತಿದ್ದರೂ ಪರೀಕ್ಷೆ ಸಮಯದಲ್ಲಿ ನೋಡುವುದು ಸರಿಯಲ್ಲ. ಸಮಯದ ಅಪವ್ಯಯಕ್ಕೆ ಹೆಚ್ಚಾಗಿ ಆಲಸ್ಯವೇ ಕಾರಣವಾಗುತ್ತದೆ. ತಡವಾಗಿ ಎದ್ದು ಗಡಿಬಿಡಿಯಲ್ಲಿ ಹೊರಟು ಶಾಲೆಗೆ ಅಥವಾ ಕಾಲೇಜಿಗೆ ಓಡುವುದರಿಂದ ಉದ್ವಿಗ್ನತೆ ಹೆಚ್ಚಾಗುತ್ತದೆ. ಪರೀಕ್ಷೆಯ ಸಮಯದಲ್ಲಿ ರಾತ್ರಿ ಬಹಳ ಹೊತ್ತಿನವರೆಗೆ ಓದುವುದರಿಂದ ಬೆಳಗ್ಗೆ ಬೇಗ ಏಳಲಾಗದೆ ಸರಿಯಾದ ಸಮಯಕ್ಕೆ ಪರೀಕ್ಷಾ ಸ್ಥಳವನ್ನು ಸೇರಲಾಗುವುದಿಲ್ಲ. ಅಷ್ಟೇ ಅಲ್ಲ ಆ ಗಡಿಬಿಡಿಯಲ್ಲಿ ರಾತ್ರಿ ಓದಿದ್ದೆಲ್ಲಾ ಮರೆತುಹೋಗಬಹುದು. ಇದಕ್ಕೆ ಮದ್ದೆಂದರೆ ವೇಳಾಪಟ್ಟಿಯೊಂದನ್ನು ತಯಾರಿಸಿಕೊಂಡು ಅದನ್ನು ಅನುಸರಿಸುವುದು. ಇದರಿಂದ ಯಾವ ಕೆಲಸವನ್ನು ಯಾವಾಗ, ಎಷ್ಟು ಮಾಡಬೇಕೆಂಬುದು ತಿಳಿಯುತ್ತದೆ. ಪ್ರಶ್ನೆಗಳು : ಅ. ವಿದ್ಯಾರ್ಥಿಗಳು ಪರೀಕ್ಷಾ ಸಮಯದಲ್ಲಿ ತಡವಾಗಿ ಏಳುವುದರಿಂದಾಗುವ ಪರಿಣಾಮವನ್ನು ತಿಳಿಸಿ. ಆ. ವೇಳೆಯನ್ನು ಬಂಡವಾಳ ಹೂಡಿಕೆಗೆ ಏಕೆ ಹೋಲಿಸಿದ್ದಾರೆ?</t>
+  </si>
+  <si>
+    <t>ನಿಮ್ಮನ್ನು ಗದಗದ ಸರ್ಕಾರಿ ಪ್ರೌಢಶಾಲೆಯ 'ಸುಪ್ರೀತ' ಎಂದು ಭಾವಿಸಿಕೊಂಡು ನಿಮ್ಮ ಮುಂದಿನ ವ್ಯಾಸಂಗಕ್ಕಾಗಿ ಜಾತಿ ಹಾಗೂ ಆದಾಯ ಪ್ರಮಾಣ ಪತ್ರವನ್ನು ಕೋರಿ ತಹಶೀಲ್ದಾರ್‌ರವರಿಗೆ ಪತ್ರವನ್ನು ಬರೆಯಿರಿ.</t>
+  </si>
+  <si>
+    <t>ಪ್ರಾಚ್ಯ ಸ್ಮಾರಕಗಳ ಸಂರಕ್ಷಣೆ. (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ಗದ್ಯಪಾಠ : 8. ಅಗ್ನಿಭೂತಿ ವಾಯುಭೂತಿಯರ ಕಥೆ</t>
+  </si>
+  <si>
+    <t>ತದ್ಧಿತಾಂತ ಭಾವನಾಮ ಪದವಿದು (ಗ್ರಹಿಕೆ-ಕಠಿಣ) (ಎ) ಬಳೆಗಾರ (ಬಿ) ಕನ್ನಡಿಗ (ಸಿ) ಜಾಣತನ (ಡಿ) ಹಾವಾಡಿಗ</t>
+  </si>
+  <si>
+    <t>ತದ್ಧಿತಾಂತಭಾವನಾಮಕ್ಕೆ ಉದಾಹರಣೆಯಾದ ಪದವಿದು (ಗ್ರಹಿಕೆ-ಕಠಿಣ) ಮಾರ್ಚ್ 2026. (ಎ) ಚೆಲುವಿಕೆ (ಬಿ) ಅಂಜಿಕೆ (ಸಿ) ಆಕೆಗಿಂತ (ಡಿ) ಸಿರಿವಂತ</t>
+  </si>
+  <si>
+    <t>ಕೊರೆತ' ಪದ ಈ ವ್ಯಾಕರಣಾಂಶಕ್ಕೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ-ಕಠಿಣ) ಮಾರ್ಚ್ 2024. (ಎ) ಕೃದಂತನಾಮ (ಬಿ) ಕೃದಂತಭಾವನಾಮ (ಸಿ) ಕೃದಂತಾವ್ಯಯ (ಡಿ) ತದ್ಧಿತಾಂತಭಾವನಾಮ</t>
+  </si>
+  <si>
+    <t>ಜಾಣತನ' ಎಂಬುದು ಈ ವ್ಯಾಕರಣಾಂಶವಾಗಿದೆ (ಸ್ಮರಣೆ-ಕಠಿಣ) ಮಾರ್ಚ್ 2025. (ಎ) ತದ್ಧಿತಾಂತಭಾವನಾಮ (ಬಿ) ತದ್ಧಿತಾಂತನಾಮ (ಸಿ) ತದ್ಧಿತಾಂತಾವ್ಯಯ (ಡಿ) ಕೃದಂತಭಾವನಾಮ</t>
+  </si>
+  <si>
+    <t>ಅಂಜಿಕೆ' ಪದ ಈ ವ್ಯಾಕರಣಾಂಶಕ್ಕೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ-ಕಠಿಣ) (ಎ) ಕೃದಂತನಾಮ (ಬಿ) ಕೃದಂತಭಾವನಾಮ (ಸಿ) ಕೃದಂತಾವ್ಯಯ (ಡಿ) ತದ್ಧಿತಾಂತಭಾವನಾಮ</t>
+  </si>
+  <si>
+    <t>ಕನ್ನಡಿಗ : ತದ್ಧಿತಾಂತನಾಮ : : ಪೆರ್ಮೆ : (ಗ್ರಹಿಕೆ-ಕಠಿಣ) ಮಾರ್ಚ್ 2026.</t>
+  </si>
+  <si>
+    <t>ನಿನಗಾಗಿ : ತದ್ಧಿತಾಂತಾವ್ಯಯ : : ಜಾಣತನ : (ಗ್ರಹಿಕೆ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ಸಿರಿತನ : ತದ್ಧಿತಾಂತಭಾವನಾಮ : : ನೆನಪು : (ಗ್ರಹಿಕೆ-ಕಠಿಣ) ಮಾರ್ಚ್ 2025.</t>
+  </si>
+  <si>
+    <t>ನೆನಪು : ಕೃದಂತಭಾವನಾಮ : : ಕಪ್ಪು : (ಗ್ರಹಿಕೆ-ಕಠಿಣ) ಮಾ-2017.</t>
+  </si>
+  <si>
+    <t>ಮಾಟ : ಕೃದಂತಭಾವನಾಮ : : ಮಾಡಿದ : (ಗ್ರಹಿಕೆ-ಕಠಿಣ) ಮೇ 2025.</t>
+  </si>
+  <si>
+    <t>ಜಾಣತನ : ತದ್ಧಿತಾಂತ ಭಾವನಾಮ : : ಚಂದ್ರನಂತೆ : (ಗ್ರಹಿಕೆ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ಬರೆದ : ಕೃದಂತನಾಮ : : ಬರೆದು : (ಗ್ರಹಿಕೆ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ಕನ್ನಡಿಗ : ತದ್ಧಿತಾಂತ ನಾಮ : : ಶಾಲೆಯವರೆಗೆ : (ಗ್ರಹಿಕೆ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ಬಾಳುವ : ವರ್ತಮಾನ ಕೃದಂತ : : ಬರೆಯದ : (ಗ್ರಹಿಕೆ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ಮಾಡಿದ : ಕೃದಂತನಾಮ : : ಮಾಟ : (ಗ್ರಹಿಕೆ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ಕೌಸಂಬಿಯ ಅರಸ ಯಾರು? (ಸ್ಮರಣೆ-ಸುಲಭ)</t>
+  </si>
+  <si>
+    <t>ಸೋಮಶರ್ಮ ಕಾಶ್ಯಪಿಯರ ಮಕ್ಕಳ ಹೆಸರೇನು? (ಸ್ಮರಣೆ-ಸುಲಭ)</t>
+  </si>
+  <si>
+    <t>ಕಾಶ್ಯಪಿ ವಿದ್ಯಾಭ್ಯಾಸಕ್ಕಾಗಿ ತನ್ನ ಮಕ್ಕಳನ್ನು ಯಾರ ಬಳಿಗೆ ಕಳುಹಿಸಿದಳು? (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2026.</t>
+  </si>
+  <si>
+    <t>ಸೂರ್ಯಮಿತ್ರನು ತನಗೆ ಕಾಶ್ಯಪಿಯೆಂಬ ತಂಗಿಯಿಲ್ಲ ಎಂದು ಹೇಳಲು ಕಾರಣವೇನು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2025, ಮೇ 2025.</t>
+  </si>
+  <si>
+    <t>ಪಂಡಿತರಾದ ಅಗ್ನಿಭೂತಿ ವಾಯುಭೂತಿಯರಿಗೆ ದೊರೆತ ಪದವಿ ಯಾವುದು? (ಸ್ಮರಣೆ-ಸುಲಭ)</t>
+  </si>
+  <si>
+    <t>ರಾಜಗೃಹ ಪಟ್ಟಣದ ಅರಸ ಯಾರು? (ಸ್ಮರಣೆ-ಸುಲಭ)</t>
+  </si>
+  <si>
+    <t>ರಾಜಸಭೆಯಲ್ಲಿ ಅಗ್ನಿಭೂತಿ ವಾಯುಭೂತಿಯರನ್ನು ಮೂರ್ಖರೆಂದು ತೀರ್ಮಾನಿಸಿದ್ದೇಕೆ? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2026. (ಕ.ಫ-3)</t>
+  </si>
+  <si>
+    <t>ಅಗ್ನಿಭೂತಿ ವಾಯುಭೂತಿಯರು ಸೂರ್ಯಮಿತ್ರನಿಂದ ಕಲಿತ ವಿದ್ಯೆಗಳಾವುವು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)</t>
+  </si>
+  <si>
+    <t>ಸೂರ್ಯಮಿತ್ರನು ಅಗ್ನಿಭೂತಿ ವಾಯುಭೂತಿಯರಿಗೆ ವಿದ್ಯಾಭ್ಯಾಸದ ನಂತರ ಮಾವನೆಂದು ಹೇಳಲು ಕಾರಣವೇನು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-3)</t>
+  </si>
+  <si>
+    <t>ಸೂರ್ಯಮಿತ್ರನು ಮಾವನೆಂದು ತಿಳಿದಾಗ ವಾಯುಭೂತಿಯ ಪ್ರತಿಕ್ರಿಯೆ ಹೇಗಿತ್ತು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮೇ 2025. (ಕ.ಫ-3)</t>
+  </si>
+  <si>
+    <t>ಶಿವಕೋಟ್ಯಾಚಾರ್ಯ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ಕೈಕೆಸರಾದರೆ ಬಾಯಿ ಮೊಸರು. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಜೂನ್ 2019.</t>
+  </si>
+  <si>
+    <t>“ಕಣ್ಣ ನೀರಂ ತೀವಿ ನೆಲನಂ ಬರೆಯುತ್ತಿರೆ" (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>“ವಿದ್ಯಾರ್ಥಿಗಳಾಗಿಯೋದಂ ಕಲೆಮೆಂಬಳಿಯೊಳ್ ಬಂದಿರಪ್ಪೊಡೆ” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ) ಮಾರ್ಚ್ 2025.</t>
+  </si>
+  <si>
+    <t>"ಪಸರಂಗೊಟ್ಟೆನಿಲ್ಲಿದರ್ಕ್ಕೆ ಮುಳಿಯದಿರಿಂ" (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>"ಪಂಡಿತಜನಮೆಲ್ಲಮೆಚ್ಚಿ ಬಿಚ್ಚಳಿಸಿ" (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)</t>
+  </si>
+  <si>
+    <t>ಸಪ್ತವ್ಯಸನಿಗಳಾಗಿದ್ದ ಅಗ್ನಿಭೂತಿ ವಾಯುಭೂತಿಯರು ಪಂಡಿತರಾದ ಬಗೆಯನ್ನು ನಿಮ್ಮ ಮಾತುಗಳಲ್ಲಿ ಬರೆಯಿರಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ಸೂರ್ಯಮಿತ್ರನು ತಮ್ಮ ಮಾವನೆಂದು ತಿಳಿದಾಗ ಅಗ್ನಿಭೂತಿ ವಾಯುಭೂತಿಯರಲ್ಲಿ ಮೂಡಿದ ಭಾವನೆಗಳನ್ನು ವಿವರಿಸಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)</t>
+  </si>
+  <si>
+    <t>ಭಾರತೀಯ ಕ್ರಿಕೆಟಿನ ಯಶಸ್ಸಿನ ಹಿಂದೆ ನೂರಾರು ಖ್ಯಾತನಾಮರು ಇದ್ದಾರೆ. ಅವರಲ್ಲಿ ಕರ್ನಾಟಕದ ರಾಹುಲ್ ದ್ರಾವಿಡ್ ಸಹ ಒಬ್ಬರು. 'ಬೆಳೆಯುವ ಸಿರಿ ಮೊಳಕೆಯಲ್ಲಿ' ಎಂಬ ಮಾತು ರಾಹುಲ್ ದ್ರಾವಿಡ್ ಅವರಿಗೆ ಸೊಗಸಾಗಿ ಅನ್ವಯವಾಗುತ್ತದೆ. ಅವರು ಬಾಲ್ಯದಲ್ಲಿಯೇ ಕ್ರಿಕೆಟ್ ಆಟದಲ್ಲಿ ಆಸಕ್ತಿಹೊಂದಿ ಸತತ ಅಭ್ಯಾಸ ಮಾಡುತ್ತಿದ್ದರು. ಅದರ ಫಲವಾಗಿ ತಮ್ಮ ಹನ್ನೆರಡನೆಯ ವಯಸ್ಸಿನಲ್ಲಿಯೇ ಶಾಲಾತಂಡವನ್ನು ಪ್ರತಿನಿಧಿಸುವಂತಾಯಿತು. ಆಡಿದ ಮೊದಲ ಪಂದ್ಯದಲ್ಲಿಯೇ ಶತಕವನ್ನು ಬಾರಿಸಿದರು. ಒಂದು ಉತ್ತಮವಾದ ಎಸೆತವು ಪ್ರಸಿದ್ಧ ಆಟಗಾರನನ್ನಾದರೂ ಔಟ್ ಮಾಡಬಹುದು. ಆದರೆ ರಾಹುಲ್ ದ್ರಾವಿಡ್ ಅವರದ್ದು ಬಹುತೇಕ ಎಲ್ಲಾ ರೀತಿಯ ಎಸೆತಗಳನ್ನು ನಿಭಾಯಿಸುವ, ವಿಕೇಟನ್ನು ಒಪ್ಪಿಸದಿರುವ, ಸಾವಕಾಶವಾಗಿ ರನ್ ಗಳಿಸುವ ಅದ್ವಿತೀಯ ಬ್ಯಾಟಿಂಗ್ ಶೈಲಿ. ದಿನವಿಡಿ ಕ್ರೀಸಿನಲ್ಲಿ ನಿಲ್ಲಬಲ್ಲ ಸಾಮರ್ಥ್ಯ ಅವರದ್ದು. ಅದೇ ಅವರನ್ನು 'ಗೋಡೆ' ಎಂಬ ಅನ್ವರ್ಥನಾಮದಿಂದ ಪ್ರಸಿದ್ಧರನ್ನಾಗಿಸಿತು. ಬೌಂಡರಿ ಬಾರಿಸು ಅಥವಾ ಔಟಾಗು ಎಂಬ ಮನೋಭಾವದ ಆಟಗಾರರಿಗಿಂತ ಭಿನ್ನವಾದ ಶೈಲಿ ರಾಹುಲ್ ಅವರದ್ದು. ಸಂಯಮದ ಹೊಡೆತ, ಉತ್ತಮ ಎಸೆತವನ್ನು ಗೌರವಿಸುವುದು, ಕೆಟ್ಟ ಎಸೆತವನ್ನು ಅಷ್ಟೇ ನಿರ್ದಾಕ್ಷಿಣ್ಯವಾಗಿ ಶಿಕ್ಷಿಸುವುದು, ಎಲ್ಲ ಬಗೆಯ ಹೊಡೆತಗಳಲ್ಲೂ ಶಿಸ್ತು, ಕಲಾತ್ಮಕತೆ, ಎಲ್ಲವೂ ನಯನ ಮನೋಹರ. ಇವು ರಾಹುಲ್ ದ್ರಾವಿಡ್ ಅವರ ಕ್ರಿಕೆಟ್ ಆಟದ ವೈಶಿಷ್ಟ್ಯವಾಗಿತ್ತು. ರಾಹುಲ್ ದ್ರಾವಿಡ್ ಅವರು ಎಂದೂ ಸ್ವಂತ ದಾಖಲೆಗಾಗಿ ಆಡಿದವರಲ್ಲ; ತಂಡದ ಗೆಲುವಿಗಾಗಿ; ದೇಶದ ಗೌರವಕ್ಕಾಗಿ ಆಡಿದವರು. ಪ್ರಶ್ನೆಗಳು : ಅ. ರಾಹುಲ್ ದ್ರಾವಿಡ್ ಅವರನ್ನು 'ಗೋಡೆ' ಎಂದು ಕರೆಯಲು ಕಾರಣವೇನು? ಆ. ರಾಹುಲ್ ದ್ರಾವಿಡ್ ಅವರ ಕ್ರಿಕೆಟ್ ಆಟದ ವೈಶಿಷ್ಟ್ಯಗಳೇನು?</t>
+  </si>
+  <si>
+    <t>ನಿಮ್ಮನ್ನು ಹಾವೇರಿಯ ಸರ್ಕಾರಿ ಪ್ರೌಢಶಾಲೆಯ 'ಮೇಘಾ' ಎಂದು ಭಾವಿಸಿಕೊಂಡು ಮೈಸೂರಿನ ಕೆ. ಆರ್. ಎಸ್. ಬೃಂದಾವನಕ್ಕೆ ಪ್ರವೇಶ ಬಯಸಿ ಅಲ್ಲಿನ ವ್ಯವಸ್ಥಾಪಕರಿಗೆ ಪತ್ರವನ್ನು ಬರೆಯಿರಿ.</t>
+  </si>
+  <si>
+    <t>ಅಕ್ಷರ ದಾಸೋಹ ಮತ್ತು ಕ್ಷೀರ ಭಾಗ್ಯಗಳ ಸಾಮಾಜಿಕ ಮಹತ್ತ್ವ. (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ) ಮಾರ್ಚ್ 2026, 2025.</t>
+  </si>
+  <si>
+    <t>ಪದ್ಯಪಾಠ : 1. ಸಂಕಲ್ಪಗೀತೆ</t>
+  </si>
+  <si>
+    <t>ಪೂಜಾರಿ' ಪದ ಈ ವ್ಯಾಕರಣಾಂಶಕ್ಕೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ- ಸುಲಭ) (ಎ) ರೂಢನಾಮ (ಬಿ) ಅಂಕಿತನಾಮ (ಸಿ) ಅನ್ವರ್ಥನಾಮ (ಡಿ) ಸರ್ವನಾಮ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಇನಿತು' ಪದ ನಾಮಪದದ ಈ ಪ್ರಕಾರಕ್ಕೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ- ಸುಲಭ) (ಎ) ಗುಣವಾಚಕ (ಬಿ) ಸಂಖ್ಯಾವಾಚಕ (ಸಿ) ಭಾವವಾಚಕ (ಡಿ) ಪರಿಮಾಣವಾಚಕ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಆತ್ಮಾರ್ಥಕ ಸರ್ವನಾಮಕ್ಕೆ ಉದಾಹರಣೆಯಾದ ಪದವಿದು (ಗ್ರಹಿಕೆ- ಸುಲಭ) (ಎ) ತನ್ನ (ಬಿ) ಏನು? (ಸಿ) ನಾನು (ಡಿ) ಯಾರು?[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ರೂಢನಾಮವಲ್ಲದ ಪದವಿದು (ಗ್ರಹಿಕೆ- ಸುಲಭ) (ಎ) ನದಿ (ಬಿ) ಪರ್ವತ (ಸಿ) ಊರು (ಡಿ) ಸಹದೇವ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಅಂಕಿತನಾಮಕ್ಕೆ ಉದಾಹರಣೆಯಾದ ಪದವಿದು (ಗ್ರಹಿಕೆ- ಸುಲಭ) (ಎ) ಮನುಷ್ಯ (ಬಿ) ದೇಶ (ಸಿ) ಕಮಲಾಕ್ಷ (ಡಿ) ವಿದ್ವಾಂಸ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಅನ್ವರ್ಥನಾಮ ಪದವಿದು (ಗ್ರಹಿಕೆ- ಸುಲಭ) (ಎ) ಮನುಷ್ಯ (ಬಿ) ದೇಶ (ಸಿ) ಕಮಲಾಕ್ಷ (ಡಿ) ವಿದ್ವಾಂಸ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಗುಣವಾಚಕ ಪದಕ್ಕೆ ಸೇರಿದ ಪದವಿದು (ಗ್ರಹಿಕೆ- ಸುಲಭ) (ಎ) ಹಳತು (ಬಿ) ಎಂಭತ್ತು (ಸಿ) ಮೂವರು (ಡಿ) ತೆಂಕಣ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಪರಿಮಾಣವಾಚಕಕ್ಕೆ ಉದಾಹರಣೆಯಾದ ಪದವಿದು (ಗ್ರಹಿಕೆ-ಸುಲಭ) (ಎ) ಮಾಟ (ಬಿ) ಪಡುವಣ (ಸಿ) ಅನಿತು (ಡಿ) ಹಿರಿಮೆ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ತುಸು' ಪದದಲ್ಲಿರುವ ವ್ಯಾಕರಣಾಂಶ (ಸಾಧಾರಣ- ಸುಲಭ) (ಎ) ಪರಿಮಾಣವಾಚಕ (ಬಿ) ದಿಗ್ವಾಚಕ (ಸಿ) ಗುಣವಾಚಕ (ಡಿ) ಸಂಖ್ಯಾವಾಚಕ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ವ್ಯಾಪಾರಿ' ಪದವು ನಾಮಪದದ ಈ ಗುಂಪಿಗೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ- ಸುಲಭ) ಜೂನ್ 2023. (ಎ) ಭಾವನಾಮ (ಬಿ) ರೂಢನಾಮ (ಸಿ) ಅನ್ವರ್ಥನಾಮ (ಡಿ) ಅಂಕಿತನಾಮ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಒಳ್ಳೆಯ : ಗುಣವಾಚಕ : : ತೆಂಕಣ : (ಗ್ರಹಿಕೆ- ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನಾನು : ಉತ್ತಮಪುರುಷ : : ಅವರು : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನೀವು : ಮಧ್ಯಮಪುರುಷ : : ಅವು : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಐವತ್ತು : ಸಂಖ್ಯಾವಾಚಕ : : ಐವರು : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನದಿ : ರೂಢನಾಮ : : ವಿಜ್ಞಾನಿ : (ಗ್ರಹಿಕೆ- ಸುಲಭ) ಆಗಸ್ಟ್ 2024, ಜೂನ್ 2026.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನಾನು : ಪುರುಷಾರ್ಥಕ ಸರ್ವನಾಮ : : ಯಾರು : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಅಷ್ಟು : ಪರಿಮಾಣವಾಚಕ : : ಹನ್ನೆರಡು : (ಗ್ರಹಿಕೆ- ಸುಲಭ) ಮಾರ್ಚ್ 2026.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹನ್ನೆರಡು : ಸಂಖ್ಯಾವಾಚಕ : : ಮೂಡಣ : (ಗ್ರಹಿಕೆ- ಸುಲಭ) ಸೆಪ್ಟೆಂಬರ್ 2020.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಪರ್ವತ : ರೂಢನಾಮ : : ಧರ್ಮರಾಯ : (ಗ್ರಹಿಕೆ- ಸುಲಭ) ಮಾರ್ಚ್ 2023.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಪರ್ವತ : ರೂಢನಾಮ : : ವಿದ್ವಾಂಸ : (ಗ್ರಹಿಕೆ- ಸುಲಭ) ಜೂನ್ 2024.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಪ್ರೀತಿಯ ಹಣತೆಯನ್ನು ಎಲ್ಲಿ ಹಚ್ಚಬೇಕೆಂದು ಕವಿ ಶಿವರುದ್ರಪ್ಪನವರು ಹೇಳಿದ್ದಾರೆ? (ಸ್ಮರಣೆ - ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕವಿ ಶಿವರುದ್ರಪ್ಪನವರು ಯಾವುದನ್ನು ಎಚ್ಚರದಲಿ ಮುನ್ನಡೆಸಬೇಕು ಎಂದು ಹೇಳಿದ್ದಾರೆ? (ಸ್ಮರಣೆ - ಸುಲಭ) ಮಾರ್ಚ್ 2024.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನದೀಜಲಗಳು ಏನಾಗಿವೆ? (ಸ್ಮರಣೆ - ಸುಲಭ) ಮಾರ್ಚ್ 2022[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕವಿ ಶಿವರುದ್ರಪ್ಪನವರು ಯಾವುದಕ್ಕೆ ಮುಂಗಾರಿನ ಮಳೆಯಾಗಬೇಕೆಂದು ಹೇಳಿದ್ದಾರೆ? (ಸ್ಮರಣೆ - ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕಾಡುಮೇಡುಗಳ ಸ್ಥಿತಿ ಹೇಗಿದೆ? (ಗ್ರಹಿಕೆ - ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕವಿ ಶಿವರುದ್ರಪ್ಪನವರು ವಸಂತವಾಗುತ ಏನನ್ನು ಮುಟ್ಟಬೇಕಿದೆ ಎಂದಿದ್ದಾರೆ? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಬಿದ್ದುದನ್ನು ಮೇಲೆಬ್ಬಿಸಿ ನಿಲ್ಲಿಸಿ ಕವಿ ಏನನ್ನು ಕಟ್ಟೋಣವೆಂದು ತಿಳಿಸುತ್ತಾರೆ? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಮನುಜರ ನಡುವಿನ ಅಡ್ಡಗೋಡೆಗಳ ಕೆಡವುತ ಏನಾಗಬೇಕೆಂದು ಕವಿ ಬಯಸಿದ್ದಾರೆ? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕವಿ ಶಿವರುದ್ರಪ್ಪನವರು ಯಾವ ಎಚ್ಚರದೊಳು ಬದುಕಬೇಕಿದೆ ಎಂದು ಹೇಳಿದ್ದಾರೆ? (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2024.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನಾಳಿನ ಕನಸನ್ನು ಎಲ್ಲಿ ಬಿತ್ತಬೇಕು ಎಂದು ಕವಿ ಜಿ. ಎಸ್. ಶಿವರುದ್ರಪ್ಪನವರು ಹೇಳಿದ್ದಾರೆ? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಡಗನ್ನು ಯಾವುದರ ಬೆಳಕಿನಲ್ಲಿ ಮುನ್ನಡೆಸಬೇಕೆಂಬುದು ಕವಿ ಶಿವರುದ್ರಪ್ಪನವರ ಅಭಿಪ್ರಾಯವಾಗಿದೆ? (ಗ್ರಹಿಕೆ-ಸುಲಭ) (ಕ.ಫ-2)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಬರಡಾಗಿರುವ ಕಾಡುಮೇಡುಗಳನ್ನು ಹೇಗೆ ಮುಟ್ಟಬೇಕಿದೆ' ಎಂದು ಕವಿ ಹೇಳಿದ್ದಾರೆ? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-3)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹೊಸ ಭರವಸೆಗಳನ್ನು ಮೂಡಿಸಿ ಯಾವುದರ ನಡುವೆ ಸೇತುವೆಯಾಗಬೇಕಿದೆ ಎಂದು ಕವಿ ಶಿವರುದ್ರಪ್ಪನವರು ವಿವರಿಸಿದ್ದಾರೆ? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2024. (ಕ.ಫ-3)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕವಿ ಜಿ. ಎಸ್. ಶಿವರುದ್ರಪ್ಪನವರು ನಾಳಿನ ಕನಸನ್ನು ಬಿತ್ತಬೇಕಾದರೆ ನಾವು ಹೇಗೆ ಬದುಕಬೇಕೆಂದಿದ್ದಾರೆ? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಆಗಸ್ಟ್ 2024. (ಕ.ಫ-3)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕೆಳಗಿನ ಕವಿಯ ಜನ್ಮಸ್ಥಳ, ಕಾಲ, ಕೃತಿ ಮತ್ತು ಪ್ರಶಸ್ತಿಗಳನ್ನು ಕುರಿತು ವಾಕ್ಯರೂಪದಲ್ಲಿ ಬರೆಯಿರಿ :</t>
+  </si>
+  <si>
+    <t>ಜಿ. ಎಸ್. ಶಿವರುದ್ರಪ್ಪ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2023, ಸೆಪ್ಟೆಂಬರ್ 2020.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಗೀಜಗನ ಗೂಡುಗಳು ತೊಟ್ಟಿಲಿನಂತೆ ತೂಗಾಡುತ್ತಿದ್ದವು.” (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2026.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಬಾನಿನಲ್ಲಿ ಗಾಳಿಪಟಗಳು ಹಕ್ಕಿಗಳಂತೆ ಹಾರಾಡುತ್ತಿದ್ದವು.” (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಪ್ರೀತಿಯ ಹಣತೆಯ ಹಚ್ಚೋಣ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2022, ಆಗಸ್ಟ್ 2024[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಮುಂಗಾರಿನ ಮಳೆಯಾಗೋಣ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಹೊಸ ಭರವಸೆಗಳ ಕಟ್ಟೋಣ” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಹೊಸ ಎಚ್ಚರದೊಳು ಬದುಕೋಣ” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಎಚ್ಚರದಲಿ ಮುನ್ನಡೆಸೋಣ” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ವಸಂತವಾಗುತ ಮುಟ್ಟೋಣ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2020.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಕೆಡವುತ ಸೇತುವೆಯಾಗೋಣ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ನಾಳಿನ ಕನಸನು ಬಿತ್ತೋಣ” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕೆಳಗಿನ ಪದ್ಯಭಾಗವನ್ನು ಪೂರ್ಣಗೊಳಿಸಿ ಬರೆಯಿರಿ :</t>
+  </si>
+  <si>
+    <t>ಕಲುಷಿತವಾದೀ ......................... ಮುಟ್ಟೋಣ. ಅಥವಾ ಮತಗಳೆಲ್ಲವೂ ......................... ಬಿತ್ತೋಣ. (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2022, 2026. (ಕ.ಫ-17)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕೆಳಗಿನ ಪದ್ಯಭಾಗವನ್ನು ಓದಿ ಅರ್ಥಮಾಡಿಕೊಂಡು, ಅಡಕವಾಗಿರುವ ಮೌಲ್ಯವನ್ನಾಧರಿಸಿ ಸಾರಾಂಶ ಬರೆಯಿರಿ :</t>
+  </si>
+  <si>
+    <t>ಸುತ್ತಲು ಕವಿಯುವ ಕತ್ತಲೆಯೊಳಗೆ ಪ್ರೀತಿಯ ಹಣತೆಯ ಹಚ್ಚೋಣ ಬಿರುಗಾಳಿಗೆ ಹೊಯ್ದಾಡುವ ಹಡಗನು ಎಚ್ಚರದಲಿ ಮುನ್ನಡೆಸೋಣ - ಮೇ 2025.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕಲುಷಿತವಾದೀ ನದೀಜಲಗಳಿಗೆ ಮುಂಗಾರಿನ ಮಳೆಯಾಗೋಣ ಬರಡಾಗಿರುವೀ ಕಾಡುಮೇಡುಗಳ ವಸಂತವಾಗುತ ಮುಟ್ಟೋಣ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಬಿದ್ದುದನ್ನು ಮೇಲೆಬ್ಬಿಸಿ ನಿಲ್ಲಿಸಿ ಹೊಸಭರವಸೆಗಳ ಕಟ್ಟೋಣ ಮನುಜರ ನಡುವಣ ಅಡ್ಡಗೋಡೆಗಳ ಕೆಡವುತ ಸೇತುವೆಯಾಗೋಣ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಮತಗಳೆಲ್ಲವು ಪಥಗಳು ಎನ್ನುವ ಹೊಸ ಎಚ್ಚರದೊಳು ಬದುಕೋಣ ಭಯ ಸಂಶಯದೊಳು ಕಂದಿದ ಕಣ್ಣೊಳು ನಾಳಿನ ಕನಸನು ಬಿತ್ತೋಣ - ಜೂನ್ 2024.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನಾವು ಯಾವ ಸಂಕಲ್ಪ ಕೈಗೊಳ್ಳಬೇಕೆಂಬುದು ಕವಿ ಶಿವರುದ್ರಪ್ಪನವರ ಆಶಯವಾಗಿದೆ? ಬರೆಯಿರಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2025, ಜೂನ್ 2023.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಸಂಕಲ್ಪ ಮತ್ತು ಅನುಷ್ಠಾನದ ಕುರಿತು ಕವಿ ಶಿವರುದ್ರಪ್ಪನವರ ಅಭಿಪ್ರಾಯವನ್ನು ವಿವರಿಸಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2025, ಜೂನ್ 2023.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಪದ್ಯಪಾಠ : 2. ಹಕ್ಕಿ ಹಾರುತಿದೆ ನೋಡಿದಿರಾ</t>
+  </si>
+  <si>
+    <t>ಬೇಗನೆ' ಪದ ಈ ಅವ್ಯಯಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2022, 2024. (ಎ) ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ (ಬಿ) ಅನುಕರಣಾವ್ಯಯ (ಸಿ) ಭಾವಸೂಚಕಾವ್ಯಯ (ಡಿ) ಕ್ರಿಯಾರ್ಥಕಾವ್ಯಯ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಲವು ವಸ್ತುಗಳಲ್ಲಿ ಒಂದನ್ನು ನಿಶ್ಚಯವಾಗಿ ಹೇಳುವ ಸಂದರ್ಭದಲ್ಲಿ ಈ ಅವ್ಯಯವನ್ನು ಬಳಸಲಾಗುವುದು (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2017, 2019. (ಎ) ಸಂಬಂಧಾರ್ಥಕಾವ್ಯಯ (ಬಿ) ಭಾವಸೂಚಕಾವ್ಯಯ (ಸಿ) ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ (ಡಿ) ಅವಧಾರಣಾರ್ಥಕಾವ್ಯಯ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಸಾಕು' ಪದವು ಈ ಅವ್ಯಯಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2018. (ಎ) ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ (ಬಿ) ಅನುಕರಣಾವ್ಯಯ (ಸಿ) ಭಾವಸೂಚಕಾವ್ಯಯ (ಡಿ) ಕ್ರಿಯಾರ್ಥಕಾವ್ಯಯ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಅವರೇ' ಪದವು ಈ ಅವ್ಯಯಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2020. (ಎ) ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ (ಬಿ) ಕ್ರಿಯಾರ್ಥಕಾವ್ಯಯ (ಸಿ) ಸಂಬಂಧಾರ್ಥಕಾವ್ಯಯ (ಡಿ) ಅವಧಾರಣಾರ್ಥಕಾವ್ಯಯ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ರೊಯ್ಯನೆ, ಸುಯ್ಯನೆ ಪದಗಳು ಈ ಅವ್ಯಯಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿವೆ (ಸ್ಮರಣೆ-ಸುಲಭ) ಸೆಪ್ಟೆಂಬರ್ 2020. (ಎ) ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ (ಬಿ) ಅನುಕರಣಾವ್ಯಯ (ಸಿ) ಅವಧಾರಣಾರ್ಥಕಾವ್ಯಯ (ಡಿ) ಕ್ರಿಯಾರ್ಥಕಾವ್ಯಯ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಯಾವುದಾದರೊಂದು ಕ್ರಿಯೆ ನಡೆದ ರೀತಿಯನ್ನು ಹೇಳುವ ಅವ್ಯಯಗಳನ್ನು ಹೀಗೆನ್ನುವರು (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2021, ಜೂನ್ 2018. (ಎ) ಅವಧಾರಣಾರ್ಥಕಾವ್ಯಯ (ಬಿ) ಅನುಕರಣಾವ್ಯಯ (ಸಿ) ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ (ಡಿ) ಕ್ರಿಯಾರ್ಥಕಾವ್ಯಯ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಧಗಧಗ' ಪದವು ಈ ಅವ್ಯಯಕ್ಕೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2023. (ಎ) ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ (ಬಿ) ಅನುಕರಣಾವ್ಯಯ (ಸಿ) ಭಾವಸೂಚಕಾವ್ಯಯ (ಡಿ) ಕ್ರಿಯಾರ್ಥಕಾವ್ಯಯ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕ್ರಿಯಾರ್ಥಕಾವ್ಯಯಕ್ಕೆ ಉದಾಹರಣೆಯಾದ ಪದವಿದು (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2015. (ಎ) ಉಂಟು (ಬಿ) ಬೇಗನೆ (ಸಿ) ಮತ್ತು (ಡಿ) ಧಗಧಗ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಸೊಗಸಾಗಿ' ಪದವು ಅವ್ಯಯದ ಈ ಗುಂಪಿಗೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2017, ಜೂನ್ 2019. (ಎ) ಕ್ರಿಯಾರ್ಥಕಾವ್ಯಯ (ಬಿ) ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ (ಸಿ) ಅನುಕರಣಾವ್ಯಯ (ಡಿ) ಅವಧಾರಣಾರ್ಥಕಾವ್ಯಯ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನೀನೇ' ಪದವು ಈ ಅವ್ಯಯಕ್ಕೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಜೂನ್ 2017. (ಎ) ಅವಧಾರಣಾರ್ಥಕಾವ್ಯಯ (ಬಿ) ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ (ಸಿ) ಸಂಬಂಧಾರ್ಥಕಾವ್ಯಯ (ಡಿ) ಭಾವಸೂಚಕಾವ್ಯಯ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಅಥವಾ : ಸಂಬಂಧಾರ್ಥಕಾವ್ಯಯ : : ಚಟಚಟ : (ಗ್ರಹಿಕೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ತರುವಾಯ : ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ : : ಉಂಟು : (ಗ್ರಹಿಕೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಸುಮ್ಮನೆ : ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ : : ಸರಸರನೆ : (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2025.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಸಾಕು : ಕ್ರಿಯಾರ್ಥಕಾವ್ಯಯ : : ಅದುವೇ : (ಗ್ರಹಿಕೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಬೇಗನೆ : ಸಾಮಾನ್ಯಾರ್ಥಕಾವ್ಯಯ : : ಘುಳುಘುಳು : (ಗ್ರಹಿಕೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿ ಯಾವ ವೇಗದಲ್ಲಿ ಹಾರುತ್ತಿದೆ? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯ ಗರಿಯಲ್ಲಿ ಯಾವ ಬಣ್ಣಗಳಿವೆ? (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2018, 2020, 2025.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯ ಕಣ್ಣುಗಳು ಯಾವುವು? (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2015, 2023.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯು ಯಾರ ನೆತ್ತಿಯನ್ನು ಕುಕ್ಕಿದೆ? (ಸ್ಮರಣೆ-ಸುಲಭ) ಜೂನ್ 2024, ಆಗಸ್ಟ್ 2024.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯು ಯಾರನ್ನು ಹರಸಿದೆ? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯು ಯಾವುದರ ಸಂಕೇತವಾಗಿದೆ? (ಸ್ಮರಣೆ-ಸುಲಭ) ಜೂನ್ 2018, 2019.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯ ಚುಂಚಗಳು ಎಲ್ಲಿಯವರೆಗೂ ಚಾಚಿವೆ? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯು ಎಲ್ಲಿಯ ನೀರನ್ನು ಹೀರಿದೆ? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕವಿ ಯಾವುದನ್ನು ಹಳ್ಳಿಗೆ ಹೋಲಿಸಿದ್ದಾರೆ? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯು ಯಾವುದನ್ನು ಒಡೆಯಲು ಹೊಂಚು ಹಾಕಿ ನಿಂತಿದೆ? (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯ ಹಾರಾಟವನ್ನು ಆಕಾಶಕ್ಕೆ ಹೇಗೆ ಹೋಲಿಸಿದ್ದಾರೆ? (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2025, ಜೂನ್ 2023.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹೊಸಗಾಲದ ಹಸುಮಕ್ಕಳನ್ನು ಹಕ್ಕಿ ಹೇಗೆ ಹರಸಿದೆ? (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2026.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯು ಯಾವ ಮೇರೆ ಮೀರಿ, ನೀರನು ಹೀರಿದೆ? (ಗ್ರಹಿಕೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ದ. ರಾ. ಬೇಂದ್ರೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಭೀಮ ದುರ್ಯೋಧನರು ಮದಗಜಗಳಂತೆ ಹೋರಾಡಿದರು.” (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಮರವೇರಿದ ಮರ್ಕಟನಂತೆ" (ಗ್ರಹಿಕೆ-ಕಠಿಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ರೆಕ್ಕೆಗಳೆರಡೂ ಪಕ್ಕದಲ್ಲುಂಟು" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2026.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಸಾರ್ವಭೌಮರಾ ನೆತ್ತಿಯ ಕುಕ್ಕಿ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2015, 2018, 2025.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಬಲ್ಲರು ಯಾರಾ ಹಾಕಿದ ಹೊಂಚ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಹೊಸಗಾಲದ ಹಸುಮಕ್ಕಳ ಹರಸಿ” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಜೂನ್ 2017, 2019.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಮಂಗಳ ಲೋಕದ ಅಂಗಳಕೇರಿ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2023, ಜೂನ್ 2018.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ತಿಂಗಳಿನೂರಿನ ನೀರನು ಹೀರಿ” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ) ಜೂನ್ 2024.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ರೆಕ್ಕೆಯ ಬೀಸುತ ಚೇತನಗೊಳಿಸಿ” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ) ಆಗಸ್ಟ್ 2024.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ತೇಲಿಸಿ ಮುಳುಗಿಸಿ ಖಂಡಖಂಡಗಳ” (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ) ಮಾರ್ಚ್ 2020, ಜೂನ್ 2023.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>"ಬಿಳಿ ಹೊಳೆ ಬಣ್ಣದ ಗರಿ-ಗರಿ ಉಂಟು" (ಅಭಿವ್ಯಕ್ತಿ-ಕಠಿಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>"ಮಂಡಲ-ಗಿಂಡಲಗಳ ಗಡ ಮುಕ್ಕಿ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಮುಗಿಲಿಗೆ ರೆಕ್ಕೆಗಳು ಹೊಡೆದವು ಅಣ್ಣ" (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನೀಲಮೇಘಮಂಡಲ- ......................... ಕಣ್ಣಾ ಹಕ್ಕಿ ಹಾರುತಿದೆ ನೋಡಿದಿರಾ? ಅಥವಾ ಯುಗಯುಗಗಳ ......................... ಹರಸಿ ಹಕ್ಕಿ ಹಾರುತಿದೆ ನೋಡಿದಿರಾ? (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2022, 2024, ಜೂನ್ 2022, ಮೇ 2025, ಸೆಪ್ಟೆಂಬರ್ 2020.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಇರುಳಿರುಳಳಿದು ದಿನ ದಿನ ಬೆಳಗೆ ಸುತ್ತಮುತ್ತಲೂ ಮೇಲಕೆ ಕೆಳಗೆ ಗಾವುದ ಗಾವುದ ಗಾವುದ ಮುಂದೆ ಎವೆತೆರೆದಿಕ್ಕುವ ಹೊತ್ತಿನ ಒಳಗೆ ಹಕ್ಕಿ ಹಾರುತಿದೆ ನೋಡಿದಿರಾ?[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕರಿನರೆ ಬಣ್ಣದ ಪುಚ್ಚಗಳುಂಟು ಬಿಳಿ-ಹೊಳೆ ಬಣ್ಣದ ಗರಿ-ಗರಿಯುಂಟು ಕೆನ್ನನ ಹೊನ್ನನ ಬಣ್ಣ-ಬಣ್ಣಗಳ ರೆಕ್ಕೆಗಳೆರಡೂ ಪಕ್ಕದಲುಂಟು ಹಕ್ಕಿ ಹಾರುತಿದೆ ನೋಡಿದಿರಾ?[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನೀಲಮೇಘಮಂಡಲ-ಸಮ ಬಣ್ಣ ಮುಗಿಲಿಗೆ ರೆಕ್ಕೆಗಳೊಡೆದವೊ ಅಣ್ಣಾ ಚಿಕ್ಕೆಯಮಾಲೆಯ ಸೆಕ್ಕಿಸಿಕೊಂಡು ಸೂರ್ಯ-ಚಂದ್ರರನು ಮಾಡಿದೆ ಕಣ್ಣಾ ಹಕ್ಕಿ ಹಾರುತಿದೆ ನೋಡಿದಿರಾ?[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ರಾಜ್ಯದ ಸಾಮ್ರಾಜ್ಯದ ತೆನೆ ಒಕ್ಕಿ ಮಂಡಲ-ಗಿಂಡಲಗಳ ಗಡ ಮುಕ್ಕಿ ತೇಲಿಸಿ ಮುಳುಗಿಸಿ ಖಂಡ-ಖಂಡಗಳ ಸಾರ್ವಭೌಮರಾ ನೆತ್ತಿಯ ಕುಕ್ಕಿ ಹಕ್ಕಿ ಹಾರುತಿದೆ ನೋಡಿದಿರಾ? (ಜೂನ್ 2022)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಯುಗ-ಯುಗಗಳ ಹಣೆ ಬರೆಹವ ಒರಸಿ ಮನ್ವಂತರಗಳ ಭಾಗ್ಯವ ತೆರೆಸಿ ರೆಕ್ಕೆಯ ಬೀಸುತ ಚೇತನಗೊಳಿಸಿ ಹೊಸಗಾಲದ ಹಸುಮಕ್ಕಳ ಹರಸಿ ಹಕ್ಕಿ ಹಾರುತಿದೆ ನೋಡಿದಿರಾ?[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಬೆಳ್ಳಿಯ ಹಳ್ಳಿಯ ಮೇರೆಯ ಮೀರಿ ತಿಂಗಳಿನೂರಿನ ನೀರನು ಹೀರಿ ಆಡಲು ಹಾಡಲು ತಾ ಹಾರಾಡಲು ಮಂಗಳ ಲೋಕದ ಅಂಗಳಕೇರಿ ಹಕ್ಕಿ ಹಾರುತಿದೆ ನೋಡಿದಿರಾ?[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಮುಟ್ಟಿದೆ ದಿಙ್ಮಂಡಲಗಳ ಅಂಚ ಆಚೆಗೆ ಚಾಚಿದೆ ತನ್ನಯ ಚುಂಚ ಬ್ರಹ್ಮಾಂಡಗಳನು ಒಡೆಯಲು ಎಂದೋ ಬಲ್ಲರು ಯಾರಾ ಹಾಕಿದ ಹೊಂಚ! ಹಕ್ಕಿ ಹಾರುತಿದೆ ನೋಡಿದಿರಾ?[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹಕ್ಕಿಯನ್ನು ಕಾಲಗತಿಗೆ ಹೋಲಿಸುತ್ತಾ ಕವಿ ಹೇಳಿರುವ ಮಾತುಗಳನ್ನು ಕುರಿತು ಬರೆಯಿರಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನಿಸರ್ಗದತ್ತವಾದ ಕಾಲಚಕ್ರದ ಎದುರಿನಲ್ಲಿ ಎಲ್ಲರು ತಲೆಬಾಗಲೇಬೇಕು ಎಂಬುದನ್ನು ಹಕ್ಕಿ ಹಾರುವಿಕೆಯ ಸಹಜ ಕ್ರಿಯೆಯೊಂದಿಗೆ ಕವಿ ಹೇಳಿರುವ ಮಾತುಗಳನ್ನು ಸಂಗ್ರಹಿಸಿ ಬರೆಯಿರಿ. (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಪದ್ಯಪಾಠ : 3. ಕೌರವೇಂದ್ರನ ಕೊಂದೆ ನೀನು</t>
+  </si>
+  <si>
+    <t>ದ್ವಂದ್ವ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆ ಇದು (ಗ್ರಹಿಕೆ-ಕಠಿಣ) ಮಾರ್ಚ್ 2026. (ಎ) ಮುರಾರಿ (ಬಿ) ಮಾದ್ರಮಾಗಧಯಾದವರು (ಸಿ) ಕೈಯಾನು (ಡಿ) ಮೇದಿನೀಪತಿ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಹೊಗೆದೋರು' ಪದದಲ್ಲಿರುವ ಸಮಾಸ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) (ಎ) ಅಂಶಿಸಮಾಸ (ಬಿ) ತತ್ಪುರುಷಸಮಾಸ (ಸಿ) ಕ್ರಿಯಾಸಮಾಸ (ಡಿ) ಬಹುವ್ರೀಹಿಸಮಾಸ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ದಿನಪಸುತ' ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) (ಎ) ತತ್ಪುರುಷ (ಬಿ) ಕರ್ಮಧಾರಯ (ಸಿ) ಬಹುವ್ರೀಹಿ (ಡಿ) ಗಮಕ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ತತ್ಪುರುಷ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆ ಇದು (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಎ) ಸೊರ್ಕಿ (ಬಿ) ಬಿಲ್ಗೊಂಡು (ಸಿ) ಪೂದೋಟ (ಡಿ) ಬಿಲ್ಲಿರುವನೇರಿಸಿ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಇಮ್ಮಾವು' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) (ಎ) ತತ್ಪುರುಷ (ಬಿ) ಕರ್ಮಧಾರಯ (ಸಿ) ಗಮಕ (ಡಿ) ದ್ವಂದ್ವ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಮೂಗಾವುದ' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2025. (ಎ) ಕರ್ಮಧಾರಯ (ಬಿ) ದ್ವಿಗು (ಸಿ) ಕ್ರಿಯಾ (ಡಿ) ಬಹುವ್ರೀಹಿ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕುಡಿಹುಬ್ಬು' ಈ ಪದದಲ್ಲಿರುವ ಸಮಾಸ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) (ಎ) ತತ್ಪುರುಷ (ಬಿ) ಕರ್ಮಧಾರಯ (ಸಿ) ಕ್ರಿಯಾ (ಡಿ) ಅಂಶಿ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಸಪ್ತಸ್ವರಗಳು' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) (ಎ) ದ್ವಿಗು (ಬಿ) ಕ್ರಿಯಾ (ಸಿ) ದ್ವಂದ್ವ (ಡಿ) ಕರ್ಮಧಾರಯ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಅಂಗೈ' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಆಗಸ್ಟ್ 2024 (ಎ) ತತ್ಪುರುಷ (ಬಿ) ಕ್ರಿಯಾ (ಸಿ) ದ್ವಿಗು (ಡಿ) ಅಂಶಿ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಬೆಟ್ಟದಾವರೆ' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2019, 2023, ಜೂನ್ 2022, 2026. (ಎ) ಕರ್ಮಧಾರಯ (ಬಿ) ದ್ವಿಗು (ಸಿ) ತತ್ಪುರುಷ (ಡಿ) ಗಮಕ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಮೋಸಮಾಡು' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) (ಎ) ತತ್ಪುರುಷ (ಬಿ) ಕ್ರಿಯಾ ಸಮಾಸ (ಸಿ) ದ್ವಿಗು ಸಮಾಸ (ಡಿ) ಅಂಶಿ ಸಮಾಸ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕಳ್ಳುಡಿದ' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಸೇರಿದೆ (ಸ್ಮರಣೆ -ಸಾಧಾರಣ) (ಎ) ಕ್ರಿಯಾ (ಬಿ) ಗಮಕ (ಸಿ) ಕರ್ಮಧಾರಯ (ಡಿ) ದ್ವಿಗು[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಮುಕ್ಕಣ್ಣು' ಪದದಲ್ಲಿರುವ ಸಮಾಸ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಸೆಪ್ಟೆಂಬರ್ 2020. (ಎ) ಅಂಶಿ (ಬಿ) ದ್ವಂದ್ವ (ಸಿ) ಕ್ರಿಯಾ (ಡಿ) ದ್ವಿಗು[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕ್ರಿಯಾಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆ ಇದು (ಗ್ರಹಿಕೆ-ಕಠಿಣ) ಮಾರ್ಚ್ 2021. (ಎ) ಇಮ್ಮಾವು (ಬಿ) ಕಡೆಗಣ್ಣು (ಸಿ) ಕಣ್ದೆರೆ (ಡಿ) ತಲೆನೋವು[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ತಲೆನೋವು' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2022. (ಎ) ತತ್ಪುರುಷ (ಬಿ) ಕ್ರಿಯಾ (ಸಿ) ದ್ವಂದ್ವ (ಡಿ) ದ್ವಿಗು[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕಣ್ದೆರೆ' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2024. (ಎ) ಅಂಶಿ (ಬಿ) ಕರ್ಮಧಾರಯ (ಸಿ) ಕ್ರಿಯಾ (ಡಿ) ಗಮಕ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ರಾಜೀವಸಖ' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಜೂನ್ 2024. (ಎ) ತತ್ಪುರುಷ (ಬಿ) ದ್ವಂದ್ವ (ಸಿ) ಬಹುವ್ರೀಹಿ (ಡಿ) ಗಮಕ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕಂಗೆಡು' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2015, ಮೇ 2025. (ಎ) ಗಮಕ (ಬಿ) ದ್ವಿಗು (ಸಿ) ಅಂಶಿ (ಡಿ) ಕ್ರಿಯಾ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಚಕ್ರಪಾಣಿ' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಜೂನ್ 2018. (ಕ.ಫ-7) (ಎ) ತತ್ಪುರುಷ (ಬಿ) ದ್ವಂದ್ವ (ಸಿ) ಬಹುವ್ರೀಹಿ (ಡಿ) ಗಮಕ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನೆಯ್ದವಸ್ತ್ರ' ಪದವು ಈ ಸಮಾಸಕ್ಕೆ ಉದಾಹರಣೆಯಾಗಿದೆ (ಸ್ಮರಣೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2017, 2019. (ಕ.ಫ-7) (ಎ) ತತ್ಪುರುಷ (ಬಿ) ದ್ವಂದ್ವ (ಸಿ) ಬಹುವ್ರೀಹಿ (ಡಿ) ಗಮಕ[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕಪ್ಪಡಮುಟ್ಟು : ಕ್ರಿಯಾಸಮಾಸ : : ಸಪ್ತವ್ಯಸನಗಳು : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಇಮ್ಮಾವು : ಕರ್ಮಧಾರಯಸಮಾಸ : : ಹಿಂದಲೆ : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2020.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಮಾಡಿದಡುಗೆ : ಗಮಕಸಮಾಸ : : ಬಿಲ್ಗೊಂಡು : (ಗ್ರಹಿಕೆ- ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಆಕಲ್ಲು : ಗಮಕಸಮಾಸ : : ಕಣ್ದೆರೆ : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನಡುರಾತ್ರಿ : ಅಂಶಿಸಮಾಸ : : ಹೆದ್ದೊರೆ : (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಜೂನ್ 2018.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಶ್ರೀಕೃಷ್ಣನು ಕರ್ಣನನ್ನು ರಥದಲ್ಲಿ ಹೇಗೆ ಕೂರಿಸಿಕೊಂಡನು? (ಗ್ರಹಿಕೆ-ಸುಲಭ) ಸೆಪ್ಟೆಂಬರ್ 2020.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಅಶ್ವಿನಿ ದೇವತೆಗಳ ವರಬಲದಿಂದ ಜನಿಸಿದವರು ಯಾರು? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕರ್ಣನಿಗೆ ಆಮಿಷಗಳನ್ನು ಒಡ್ಡಿದವರು ಯಾರು? (ಸ್ಮರಣೆ-ಸುಲಭ) ಜೂನ್ 2023.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕರ್ಣನು ಯಾರ ಅನುಗ್ರಹದಿಂದ ಜನಿಸಿದನು? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಧರ್ಮರಾಜನು ಯಾರ ಅನುಗ್ರಹದಿಂದ ಜನಿಸಿದನು? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಭೀಮನು ಯಾರ ಅನುಗ್ರಹದಿಂದ ಜನಿಸಿದನು? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಅರ್ಜುನನು ಯಾರ ಅನುಗ್ರಹದಿಂದ ಜನಿಸಿದನು? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಫಲುಗುಣ ಎಂದು ಯಾರನ್ನು ಕರೆಯುತ್ತಾರೆ? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ನಕುಲ ಸಹದೇವರ ತಾಯಿಯ ಹೆಸರೇನು? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕೃಷ್ಣನು ಕರ್ಣನಿಗೆ ಎಲ್ಲಿಯ ರಾಜನನ್ನಾಗಿ ಮಾಡುವೆನೆಂದು ತಿಳಿಸುತ್ತಾನೆ? (ಸ್ಮರಣೆ-ಸುಲಭ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕೃಷ್ಣನು ಕರ್ಣನ ಮನದಲ್ಲಿ ಯಾವ ರೀತಿಯಲ್ಲಿ ಭಯವನ್ನು ಬಿತ್ತಿದನು? / ಮೇದಿನಿಪತಿ ನೀನು ಎಂದು ಕೃಷ್ಣನು ಕರ್ಣನ ಮನದಲ್ಲಿ ಹೇಗೆ ಭಯವನ್ನು ಬಿತ್ತಿದನು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-3)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕುಂತಿ, ಮಾದ್ರಿಯರು ಯಾರು ಯಾರ ಅನುಗ್ರಹದಿಂದ ಮಕ್ಕಳನ್ನು ಪಡೆದರು? (ಗ್ರಹಿಕೆ-ಸುಲಭ) (ಕ.ಫ-2)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕೃಷ್ಣನು ಆಮಿಷಗಳನ್ನು ಒಡ್ಡಿದಾಗ ಕರ್ಣನ ಮನದಲ್ಲಿ ಮೂಡಿದ ಭಾವನೆಗಳಾವುವು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮೇ-2025. (ಕ.ಫ-3)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕೃಷ್ಣನು ಕೌರವೇಂದ್ರನನ್ನು ಕೊಂದನು ಎಂದು ಕರ್ಣ ಹೇಳಲು ಕಾರಣವೇನು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2022, 2024, ಜೂ-2024, ಸೆಪ್ಟೆಂಬರ್ 2024. (ಕ.ಫ-3)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಯುದ್ಧದ ವಿಚಾರದಲ್ಲಿ ಕರ್ಣನ ತೀರ್ಮಾನವನ್ನು ತಿಳಿಸಿ. (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) ಮಾರ್ಚ್ 2020. (ಕ.ಫ-3)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕೃಷ್ಣನು ಕರ್ಣನಿಗೆ ರಾಜನಾದರೆ ಹೇಗೆ ಶೋಭಿಸಬಹುದೆಂದು ತಿಳಿಸುತ್ತಾನೆ? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ದುಃಖಿತನಾದ ಕರ್ಣನನ್ನು ಕೃಷ್ಣನು ಹೇಗೆ ಸಂತೈಸಿದನು? (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) (ಕ.ಫ-2)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕೆಳಗಿನ ಕವಿಯ ಜನ್ಮಸ್ಥಳ, ಕಾಲ, ಕೃತಿ ಮತ್ತು ಬಿರುದುಗಳನ್ನು ಕುರಿತು ವಾಕ್ಯ ರೂಪದಲ್ಲಿ ಬರೆಯಿರಿ :</t>
+  </si>
+  <si>
+    <t>ಕುಮಾರವ್ಯಾಸ. (ಸ್ಮರಣೆ-ಸುಲಭ) ಮಾರ್ಚ್ 2022, 2025, ಜೂನ್ 2024, ಮೇ 2025.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>ಕೆಳಗಿನ ಪದ್ಯಭಾಗಕ್ಕೆ ಪ್ರಸ್ತಾರ ಹಾಕಿ, ಗಣ ವಿಭಾಗ ಮಾಡಿ, ಛಂದಸ್ಸಿನ ಹೆಸರನ್ನು ಬರೆಯಿರಿ :</t>
+  </si>
+  <si>
+    <t>ಲಲನೆ ಪಡೆದೀಯೈದು ಮಂತ್ರಂಗಳಲಿ ಮೊದಲಿಗ ನೀನು ನಿನ್ನಯ ಬಳಿಯುಧಿಷ್ಠಿರದೇವ ಮೂರನೆಯಾತ ಕಲಿಭೀಮ (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಮಾರಿಗೌತಣವಾಯಿತು ನಾಳಿನ ಭಾರತವು" (ಗ್ರಹಿಕೆ-ಸಾಧಾರಣ) 2024.[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>"ಅಳ್ಳಿರಿಯುತಿಪ್ಪ ಎಮ್ಮ ಒಡಲಬೇಗೆಯ ಬೆಂಕಿಯುರಿ ನಿನ್ನನಿರಿಯದೆ ಪೇಳು ವಿಶ್ವಾಮಿತ್ರ." (ಗ್ರಹಿಕೆ-ಕಠಿಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ರವಿ ಸುತನ ಕಿವಿಯಲಿ ಬಿತ್ತಿದನು ಭಯವ” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)[cite: 1, 2]</t>
+  </si>
+  <si>
+    <t>“ಬಾಯಂಬುಲಕೆ ಕೈಯಾನುವರೆ” (ಅಭಿವ್ಯಕ್ತಿ-ಸಾಧಾರಣ)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Nudi 01 e"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -857,7 +1768,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -865,39 +1776,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf xfId="0" fontId="3" quotePrefix="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf xfId="0" fontId="4" quotePrefix="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1127,22 +2070,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F232"/>
-  <sheetFormatPr customHeight="true" defaultRowHeight="18.6" defaultColWidth="12.6640625" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F526"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" customWidth="true" style="4"/>
-    <col min="2" max="2" width="21.77734375" customWidth="true" style="4"/>
-    <col min="3" max="3" width="109.21875" customWidth="true" style="4"/>
-    <col min="4" max="4" width="109" customWidth="true" style="4"/>
-    <col min="5" max="5" width="5.44140625" customWidth="true" style="4"/>
-    <col min="6" max="6" width="12.6640625" style="4"/>
+    <col min="1" max="1" width="4.7109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="109.28515625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="109" style="4" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" customHeight="1" ht="18.6" s="2" customFormat="1">
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1159,7 +2102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" customHeight="1" ht="18.6">
+    <row r="2" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1176,7 +2119,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" customHeight="1" ht="18.6">
+    <row r="3" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1193,7 +2136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" customHeight="1" ht="18.6">
+    <row r="4" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1210,7 +2153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" customHeight="1" ht="18.6">
+    <row r="5" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1227,7 +2170,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" customHeight="1" ht="18.6">
+    <row r="6" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1244,7 +2187,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" customHeight="1" ht="18.6">
+    <row r="7" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1261,7 +2204,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" customHeight="1" ht="18.6">
+    <row r="8" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1278,7 +2221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" customHeight="1" ht="18.6">
+    <row r="9" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1295,7 +2238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" customHeight="1" ht="18.6">
+    <row r="10" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1312,7 +2255,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" customHeight="1" ht="18.6">
+    <row r="11" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1329,7 +2272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" customHeight="1" ht="18.6">
+    <row r="12" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1346,7 +2289,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" customHeight="1" ht="18.6">
+    <row r="13" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1363,7 +2306,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" customHeight="1" ht="18.6">
+    <row r="14" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1380,7 +2323,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" customHeight="1" ht="18.6">
+    <row r="15" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1397,7 +2340,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" customHeight="1" ht="18.6">
+    <row r="16" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1414,7 +2357,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" customHeight="1" ht="18.6">
+    <row r="17" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1431,7 +2374,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" customHeight="1" ht="18.6">
+    <row r="18" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1448,7 +2391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" customHeight="1" ht="18.6">
+    <row r="19" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1465,7 +2408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" customHeight="1" ht="18.6">
+    <row r="20" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1482,7 +2425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" customHeight="1" ht="18.6">
+    <row r="21" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1499,7 +2442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" customHeight="1" ht="18.6">
+    <row r="22" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1516,7 +2459,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" customHeight="1" ht="18.6">
+    <row r="23" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1533,7 +2476,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:6" customHeight="1" ht="18.6">
+    <row r="24" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1550,7 +2493,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:6" customHeight="1" ht="18.6">
+    <row r="25" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1567,7 +2510,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:6" customHeight="1" ht="18.6">
+    <row r="26" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1584,7 +2527,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:6" customHeight="1" ht="18.6">
+    <row r="27" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1601,7 +2544,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:6" customHeight="1" ht="18.6">
+    <row r="28" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1618,7 +2561,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:6" customHeight="1" ht="18.6">
+    <row r="29" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1635,7 +2578,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:6" customHeight="1" ht="18.6">
+    <row r="30" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1652,7 +2595,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:6" customHeight="1" ht="18.6">
+    <row r="31" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -1669,7 +2612,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:6" customHeight="1" ht="18.6">
+    <row r="32" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -1686,7 +2629,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:6" customHeight="1" ht="18.6">
+    <row r="33" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -1703,7 +2646,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:6" customHeight="1" ht="18.6">
+    <row r="34" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1720,7 +2663,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:6" customHeight="1" ht="18.6">
+    <row r="35" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1737,7 +2680,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:6" customHeight="1" ht="18.6">
+    <row r="36" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1754,7 +2697,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:6" customHeight="1" ht="18.6">
+    <row r="37" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -1771,7 +2714,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:6" customHeight="1" ht="18.6">
+    <row r="38" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1788,7 +2731,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:6" customHeight="1" ht="18.6">
+    <row r="39" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -1805,7 +2748,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:6" customHeight="1" ht="18.6">
+    <row r="40" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -1822,7 +2765,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:6" customHeight="1" ht="18.6">
+    <row r="41" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -1839,7 +2782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:6" customHeight="1" ht="18.6">
+    <row r="42" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -1856,7 +2799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:6" customHeight="1" ht="18.6">
+    <row r="43" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -1873,7 +2816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:6" customHeight="1" ht="18.6">
+    <row r="44" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -1890,7 +2833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:6" customHeight="1" ht="18.6">
+    <row r="45" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -1907,7 +2850,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:6" customHeight="1" ht="18.6">
+    <row r="46" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -1924,7 +2867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:6" customHeight="1" ht="18.6">
+    <row r="47" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -1941,7 +2884,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:6" customHeight="1" ht="18.6">
+    <row r="48" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -1958,7 +2901,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:6" customHeight="1" ht="18.6">
+    <row r="49" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -1975,7 +2918,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:6" customHeight="1" ht="18.6">
+    <row r="50" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -1992,7 +2935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:6" customHeight="1" ht="18.6">
+    <row r="51" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -2009,7 +2952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" customHeight="1" ht="18.6">
+    <row r="52" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -2026,7 +2969,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" customHeight="1" ht="18.6">
+    <row r="53" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -2043,7 +2986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:6" customHeight="1" ht="18.6">
+    <row r="54" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -2060,7 +3003,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:6" customHeight="1" ht="18.6">
+    <row r="55" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -2077,7 +3020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:6" customHeight="1" ht="18.6">
+    <row r="56" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -2094,7 +3037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:6" customHeight="1" ht="18.6">
+    <row r="57" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -2111,7 +3054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:6" customHeight="1" ht="18.6">
+    <row r="58" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -2128,7 +3071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6" customHeight="1" ht="18.6">
+    <row r="59" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -2145,7 +3088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:6" customHeight="1" ht="18.6">
+    <row r="60" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -2162,7 +3105,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" customHeight="1" ht="18.6">
+    <row r="61" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -2179,7 +3122,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:6" customHeight="1" ht="18.6">
+    <row r="62" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -2196,7 +3139,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:6" customHeight="1" ht="18.6">
+    <row r="63" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -2213,7 +3156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:6" customHeight="1" ht="18.6">
+    <row r="64" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -2230,7 +3173,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:6" customHeight="1" ht="18.6">
+    <row r="65" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -2247,7 +3190,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66" spans="1:6" customHeight="1" ht="18.6">
+    <row r="66" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -2264,7 +3207,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:6" customHeight="1" ht="18.6">
+    <row r="67" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -2281,7 +3224,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:6" customHeight="1" ht="18.6">
+    <row r="68" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -2298,7 +3241,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:6" customHeight="1" ht="18.6">
+    <row r="69" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -2315,7 +3258,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="70" spans="1:6" customHeight="1" ht="18.6">
+    <row r="70" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -2332,7 +3275,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:6" customHeight="1" ht="18.6">
+    <row r="71" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -2349,7 +3292,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:6" customHeight="1" ht="18.6">
+    <row r="72" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -2366,7 +3309,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:6" customHeight="1" ht="18.6">
+    <row r="73" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -2383,7 +3326,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="74" spans="1:6" customHeight="1" ht="18.6">
+    <row r="74" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -2400,7 +3343,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="1:6" customHeight="1" ht="18.6">
+    <row r="75" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -2417,7 +3360,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:6" customHeight="1" ht="18.6">
+    <row r="76" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -2434,7 +3377,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:6" customHeight="1" ht="18.6">
+    <row r="77" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -2451,7 +3394,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:6" customHeight="1" ht="18.6">
+    <row r="78" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -2468,7 +3411,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="79" spans="1:6" customHeight="1" ht="18.6">
+    <row r="79" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -2485,7 +3428,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="80" spans="1:6" customHeight="1" ht="18.6">
+    <row r="80" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -2502,7 +3445,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="1:6" customHeight="1" ht="18.6">
+    <row r="81" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -2519,7 +3462,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="82" spans="1:6" customHeight="1" ht="18.6">
+    <row r="82" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -2536,7 +3479,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:6" customHeight="1" ht="18.6">
+    <row r="83" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -2553,7 +3496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:6" customHeight="1" ht="18.6">
+    <row r="84" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -2570,7 +3513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:6" customHeight="1" ht="18.6">
+    <row r="85" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -2587,7 +3530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:6" customHeight="1" ht="18.6">
+    <row r="86" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -2604,7 +3547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:6" customHeight="1" ht="18.6">
+    <row r="87" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -2621,7 +3564,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:6" customHeight="1" ht="18.6">
+    <row r="88" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -2638,7 +3581,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:6" customHeight="1" ht="18.6">
+    <row r="89" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -2655,7 +3598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:6" customHeight="1" ht="18.6">
+    <row r="90" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -2672,7 +3615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:6" customHeight="1" ht="18.6">
+    <row r="91" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -2689,7 +3632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:6" customHeight="1" ht="18.6">
+    <row r="92" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -2706,7 +3649,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:6" customHeight="1" ht="18.6">
+    <row r="93" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -2723,7 +3666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:6" customHeight="1" ht="18.6">
+    <row r="94" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -2740,7 +3683,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6" customHeight="1" ht="18.6">
+    <row r="95" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -2757,7 +3700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:6" customHeight="1" ht="18.6">
+    <row r="96" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -2774,7 +3717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:6" customHeight="1" ht="18.6">
+    <row r="97" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -2791,7 +3734,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:6" customHeight="1" ht="18.6">
+    <row r="98" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -2808,7 +3751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:6" customHeight="1" ht="18.6">
+    <row r="99" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -2825,7 +3768,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:6" customHeight="1" ht="18.6">
+    <row r="100" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -2842,7 +3785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:6" customHeight="1" ht="18.6">
+    <row r="101" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -2859,7 +3802,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:6" customHeight="1" ht="18.6">
+    <row r="102" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -2876,7 +3819,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:6" customHeight="1" ht="18.6">
+    <row r="103" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -2893,7 +3836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:6" customHeight="1" ht="18.6">
+    <row r="104" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -2910,7 +3853,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:6" customHeight="1" ht="18.6">
+    <row r="105" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -2927,7 +3870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:6" customHeight="1" ht="18.6">
+    <row r="106" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -2944,7 +3887,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:6" customHeight="1" ht="18.6">
+    <row r="107" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -2961,7 +3904,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:6" customHeight="1" ht="18.6">
+    <row r="108" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -2978,7 +3921,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:6" customHeight="1" ht="18.6">
+    <row r="109" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -2995,7 +3938,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:6" customHeight="1" ht="18.6">
+    <row r="110" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -3012,7 +3955,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="111" spans="1:6" customHeight="1" ht="18.6">
+    <row r="111" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -3029,7 +3972,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="112" spans="1:6" customHeight="1" ht="18.6">
+    <row r="112" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -3046,7 +3989,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="113" spans="1:6" customHeight="1" ht="18.6">
+    <row r="113" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -3063,7 +4006,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="114" spans="1:6" customHeight="1" ht="18.6">
+    <row r="114" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -3080,7 +4023,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="115" spans="1:6" customHeight="1" ht="18.6">
+    <row r="115" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -3097,7 +4040,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="116" spans="1:6" customHeight="1" ht="18.6">
+    <row r="116" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -3114,7 +4057,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:6" customHeight="1" ht="18.6">
+    <row r="117" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -3131,7 +4074,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:6" customHeight="1" ht="18.6">
+    <row r="118" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -3148,7 +4091,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="1:6" customHeight="1" ht="18.6">
+    <row r="119" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -3165,7 +4108,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="1:6" customHeight="1" ht="18.6">
+    <row r="120" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -3182,7 +4125,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="1:6" customHeight="1" ht="18.6">
+    <row r="121" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -3199,7 +4142,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:6" customHeight="1" ht="18.6">
+    <row r="122" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -3216,7 +4159,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="1:6" customHeight="1" ht="18.6">
+    <row r="123" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -3233,7 +4176,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="124" spans="1:6" customHeight="1" ht="18.6">
+    <row r="124" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -3250,7 +4193,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:6" customHeight="1" ht="18.6">
+    <row r="125" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -3267,7 +4210,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="126" spans="1:6" customHeight="1" ht="18.6">
+    <row r="126" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -3284,7 +4227,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="1:6" customHeight="1" ht="18.6">
+    <row r="127" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -3301,7 +4244,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="128" spans="1:6" customHeight="1" ht="18.6">
+    <row r="128" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -3318,7 +4261,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="129" spans="1:6" customHeight="1" ht="18.6">
+    <row r="129" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -3335,7 +4278,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:6" customHeight="1" ht="18.6">
+    <row r="130" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -3352,7 +4295,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="131" spans="1:6" customHeight="1" ht="18.6">
+    <row r="131" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -3369,7 +4312,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="132" spans="1:6" customHeight="1" ht="18.6">
+    <row r="132" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -3386,7 +4329,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="133" spans="1:6" customHeight="1" ht="18.6">
+    <row r="133" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -3403,7 +4346,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="134" spans="1:6" customHeight="1" ht="18.6">
+    <row r="134" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -3420,7 +4363,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="135" spans="1:6" customHeight="1" ht="18.6">
+    <row r="135" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -3437,7 +4380,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="136" spans="1:6" customHeight="1" ht="18.6">
+    <row r="136" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -3454,7 +4397,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="137" spans="1:6" customHeight="1" ht="18.6">
+    <row r="137" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -3471,7 +4414,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="138" spans="1:6" customHeight="1" ht="18.6">
+    <row r="138" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -3488,7 +4431,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="139" spans="1:6" customHeight="1" ht="18.6">
+    <row r="139" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -3505,7 +4448,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="140" spans="1:6" customHeight="1" ht="18.6">
+    <row r="140" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -3522,7 +4465,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="141" spans="1:6" customHeight="1" ht="18.6">
+    <row r="141" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -3539,7 +4482,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="142" spans="1:6" customHeight="1" ht="18.6">
+    <row r="142" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -3556,7 +4499,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="143" spans="1:6" customHeight="1" ht="18.6">
+    <row r="143" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -3573,7 +4516,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="144" spans="1:6" customHeight="1" ht="18.6">
+    <row r="144" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -3590,7 +4533,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="145" spans="1:6" customHeight="1" ht="18.6">
+    <row r="145" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>144</v>
       </c>
@@ -3607,7 +4550,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="146" spans="1:6" customHeight="1" ht="18.6">
+    <row r="146" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <v>1</v>
       </c>
@@ -3624,7 +4567,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:6" customHeight="1" ht="18.6">
+    <row r="147" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="5">
         <v>2</v>
       </c>
@@ -3641,7 +4584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="148" spans="1:6" customHeight="1" ht="18.6">
+    <row r="148" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="5">
         <v>3</v>
       </c>
@@ -3658,7 +4601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:6" customHeight="1" ht="18.6">
+    <row r="149" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="5">
         <v>4</v>
       </c>
@@ -3675,7 +4618,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:6" customHeight="1" ht="18.6">
+    <row r="150" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="5">
         <v>5</v>
       </c>
@@ -3692,7 +4635,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:6" customHeight="1" ht="18.6">
+    <row r="151" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="5">
         <v>6</v>
       </c>
@@ -3709,7 +4652,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:6" customHeight="1" ht="18.6">
+    <row r="152" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="5">
         <v>7</v>
       </c>
@@ -3726,7 +4669,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:6" customHeight="1" ht="18.6">
+    <row r="153" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="5">
         <v>8</v>
       </c>
@@ -3743,7 +4686,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:6" customHeight="1" ht="18.6">
+    <row r="154" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="5">
         <v>9</v>
       </c>
@@ -3760,7 +4703,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:6" customHeight="1" ht="18.6">
+    <row r="155" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="5">
         <v>10</v>
       </c>
@@ -3777,7 +4720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:6" customHeight="1" ht="18.6">
+    <row r="156" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="5">
         <v>11</v>
       </c>
@@ -3794,7 +4737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:6" customHeight="1" ht="18.6">
+    <row r="157" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="5">
         <v>12</v>
       </c>
@@ -3811,7 +4754,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:6" customHeight="1" ht="18.6">
+    <row r="158" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="5">
         <v>13</v>
       </c>
@@ -3828,7 +4771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:6" customHeight="1" ht="18.6">
+    <row r="159" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="5">
         <v>14</v>
       </c>
@@ -3845,7 +4788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:6" customHeight="1" ht="18.6">
+    <row r="160" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="5">
         <v>15</v>
       </c>
@@ -3862,7 +4805,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:6" customHeight="1" ht="18.6">
+    <row r="161" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <v>16</v>
       </c>
@@ -3879,7 +4822,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="162" spans="1:6" customHeight="1" ht="18.6">
+    <row r="162" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="5">
         <v>17</v>
       </c>
@@ -3896,7 +4839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="1:6" customHeight="1" ht="18.6">
+    <row r="163" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="5">
         <v>18</v>
       </c>
@@ -3913,7 +4856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="1:6" customHeight="1" ht="18.6">
+    <row r="164" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="5">
         <v>19</v>
       </c>
@@ -3930,7 +4873,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="1:6" customHeight="1" ht="18.6">
+    <row r="165" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="5">
         <v>20</v>
       </c>
@@ -3947,7 +4890,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" spans="1:6" customHeight="1" ht="18.6">
+    <row r="166" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="5">
         <v>21</v>
       </c>
@@ -3964,7 +4907,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:6" customHeight="1" ht="18.6">
+    <row r="167" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="5">
         <v>22</v>
       </c>
@@ -3981,7 +4924,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:6" customHeight="1" ht="18.6">
+    <row r="168" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="5">
         <v>23</v>
       </c>
@@ -3998,7 +4941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:6" customHeight="1" ht="18.6">
+    <row r="169" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="5">
         <v>24</v>
       </c>
@@ -4015,7 +4958,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:6" customHeight="1" ht="18.6">
+    <row r="170" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="5">
         <v>25</v>
       </c>
@@ -4032,7 +4975,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="1:6" customHeight="1" ht="18.6">
+    <row r="171" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="5">
         <v>26</v>
       </c>
@@ -4049,7 +4992,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="172" spans="1:6" customHeight="1" ht="18.6">
+    <row r="172" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="5">
         <v>27</v>
       </c>
@@ -4066,7 +5009,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="173" spans="1:6" customHeight="1" ht="18.6">
+    <row r="173" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="5">
         <v>28</v>
       </c>
@@ -4083,7 +5026,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="174" spans="1:6" customHeight="1" ht="18.6">
+    <row r="174" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="5">
         <v>29</v>
       </c>
@@ -4100,7 +5043,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="175" spans="1:6" customHeight="1" ht="18.6">
+    <row r="175" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="5">
         <v>30</v>
       </c>
@@ -4117,7 +5060,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:6" customHeight="1" ht="18.6">
+    <row r="176" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="5">
         <v>31</v>
       </c>
@@ -4134,7 +5077,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="177" spans="1:6" customHeight="1" ht="18.6">
+    <row r="177" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="5">
         <v>32</v>
       </c>
@@ -4151,7 +5094,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="1:6" customHeight="1" ht="18.6">
+    <row r="178" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="5">
         <v>33</v>
       </c>
@@ -4168,7 +5111,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="179" spans="1:6" customHeight="1" ht="18.6">
+    <row r="179" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="5">
         <v>34</v>
       </c>
@@ -4185,7 +5128,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="1:6" customHeight="1" ht="18.6">
+    <row r="180" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="5">
         <v>35</v>
       </c>
@@ -4202,7 +5145,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="1:6" customHeight="1" ht="18.6">
+    <row r="181" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="5">
         <v>36</v>
       </c>
@@ -4219,7 +5162,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="1:6" customHeight="1" ht="18.6">
+    <row r="182" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="5">
         <v>37</v>
       </c>
@@ -4236,7 +5179,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="1:6" customHeight="1" ht="18.6">
+    <row r="183" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <v>38</v>
       </c>
@@ -4253,7 +5196,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="1:6" customHeight="1" ht="18.6">
+    <row r="184" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="5">
         <v>39</v>
       </c>
@@ -4270,7 +5213,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="185" spans="1:6" customHeight="1" ht="18.6">
+    <row r="185" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="5">
         <v>40</v>
       </c>
@@ -4287,7 +5230,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="186" spans="1:6" customHeight="1" ht="18.6">
+    <row r="186" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="5">
         <v>41</v>
       </c>
@@ -4304,7 +5247,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="187" spans="1:6" customHeight="1" ht="18.6">
+    <row r="187" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="5">
         <v>42</v>
       </c>
@@ -4321,7 +5264,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="188" spans="1:6" customHeight="1" ht="18.6">
+    <row r="188" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="5">
         <v>43</v>
       </c>
@@ -4338,7 +5281,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="189" spans="1:6" customHeight="1" ht="18.6">
+    <row r="189" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="5">
         <v>44</v>
       </c>
@@ -4355,7 +5298,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="190" spans="1:6" customHeight="1" ht="18.6">
+    <row r="190" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="5">
         <v>1</v>
       </c>
@@ -4372,7 +5315,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="1:6" customHeight="1" ht="18.6">
+    <row r="191" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="5">
         <v>2</v>
       </c>
@@ -4389,7 +5332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="192" spans="1:6" customHeight="1" ht="18.6">
+    <row r="192" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="5">
         <v>3</v>
       </c>
@@ -4406,7 +5349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="193" spans="1:6" customHeight="1" ht="18.6">
+    <row r="193" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="5">
         <v>4</v>
       </c>
@@ -4423,7 +5366,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:6" customHeight="1" ht="18.6">
+    <row r="194" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="5">
         <v>5</v>
       </c>
@@ -4440,7 +5383,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="195" spans="1:6" customHeight="1" ht="18.6">
+    <row r="195" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="5">
         <v>6</v>
       </c>
@@ -4457,7 +5400,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:6" customHeight="1" ht="18.6">
+    <row r="196" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="5">
         <v>7</v>
       </c>
@@ -4474,7 +5417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:6" customHeight="1" ht="18.6">
+    <row r="197" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="5">
         <v>8</v>
       </c>
@@ -4491,7 +5434,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:6" customHeight="1" ht="18.6">
+    <row r="198" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="5">
         <v>9</v>
       </c>
@@ -4508,7 +5451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:6" customHeight="1" ht="18.6">
+    <row r="199" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="5">
         <v>10</v>
       </c>
@@ -4525,7 +5468,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:6" customHeight="1" ht="18.6">
+    <row r="200" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="5">
         <v>11</v>
       </c>
@@ -4542,7 +5485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="1:6" customHeight="1" ht="18.6">
+    <row r="201" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="5">
         <v>12</v>
       </c>
@@ -4559,7 +5502,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:6" customHeight="1" ht="18.6">
+    <row r="202" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="5">
         <v>13</v>
       </c>
@@ -4576,7 +5519,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:6" customHeight="1" ht="18.6">
+    <row r="203" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="5">
         <v>14</v>
       </c>
@@ -4593,7 +5536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="204" spans="1:6" customHeight="1" ht="18.6">
+    <row r="204" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="5">
         <v>15</v>
       </c>
@@ -4610,7 +5553,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="205" spans="1:6" customHeight="1" ht="18.6">
+    <row r="205" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="5">
         <v>16</v>
       </c>
@@ -4627,7 +5570,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="206" spans="1:6" customHeight="1" ht="18.6">
+    <row r="206" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="5">
         <v>17</v>
       </c>
@@ -4644,7 +5587,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="207" spans="1:6" customHeight="1" ht="18.6">
+    <row r="207" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="5">
         <v>18</v>
       </c>
@@ -4661,7 +5604,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="208" spans="1:6" customHeight="1" ht="18.6">
+    <row r="208" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="5">
         <v>19</v>
       </c>
@@ -4678,7 +5621,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="209" spans="1:6" customHeight="1" ht="18.6">
+    <row r="209" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="5">
         <v>20</v>
       </c>
@@ -4695,7 +5638,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="210" spans="1:6" customHeight="1" ht="18.6">
+    <row r="210" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="5">
         <v>21</v>
       </c>
@@ -4712,7 +5655,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="211" spans="1:6" customHeight="1" ht="18.6">
+    <row r="211" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="5">
         <v>22</v>
       </c>
@@ -4729,7 +5672,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="212" spans="1:6" customHeight="1" ht="18.6">
+    <row r="212" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="5">
         <v>23</v>
       </c>
@@ -4746,7 +5689,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="213" spans="1:6" customHeight="1" ht="18.6">
+    <row r="213" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="5">
         <v>24</v>
       </c>
@@ -4763,7 +5706,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="214" spans="1:6" customHeight="1" ht="18.6">
+    <row r="214" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="5">
         <v>25</v>
       </c>
@@ -4780,7 +5723,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="215" spans="1:6" customHeight="1" ht="18.6">
+    <row r="215" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="5">
         <v>26</v>
       </c>
@@ -4797,7 +5740,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="216" spans="1:6" customHeight="1" ht="18.6">
+    <row r="216" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="5">
         <v>27</v>
       </c>
@@ -4814,7 +5757,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="217" spans="1:6" customHeight="1" ht="18.6">
+    <row r="217" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="5">
         <v>28</v>
       </c>
@@ -4831,7 +5774,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="218" spans="1:6" customHeight="1" ht="18.6">
+    <row r="218" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="5">
         <v>29</v>
       </c>
@@ -4848,7 +5791,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:6" customHeight="1" ht="18.6">
+    <row r="219" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="5">
         <v>30</v>
       </c>
@@ -4865,7 +5808,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="220" spans="1:6" customHeight="1" ht="18.6">
+    <row r="220" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="5">
         <v>31</v>
       </c>
@@ -4882,7 +5825,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="221" spans="1:6" customHeight="1" ht="18.6">
+    <row r="221" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="5">
         <v>32</v>
       </c>
@@ -4899,7 +5842,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="222" spans="1:6" customHeight="1" ht="18.6">
+    <row r="222" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="5">
         <v>33</v>
       </c>
@@ -4916,7 +5859,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="223" spans="1:6" customHeight="1" ht="18.6">
+    <row r="223" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="5">
         <v>34</v>
       </c>
@@ -4933,7 +5876,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="224" spans="1:6" customHeight="1" ht="18.6">
+    <row r="224" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="5">
         <v>35</v>
       </c>
@@ -4950,7 +5893,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="225" spans="1:6" customHeight="1" ht="18.6">
+    <row r="225" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="5">
         <v>36</v>
       </c>
@@ -4967,7 +5910,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:6" customHeight="1" ht="18.6">
+    <row r="226" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="5">
         <v>37</v>
       </c>
@@ -4984,7 +5927,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:6" customHeight="1" ht="18.6">
+    <row r="227" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="5">
         <v>38</v>
       </c>
@@ -5001,7 +5944,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="228" spans="1:6" customHeight="1" ht="18.6">
+    <row r="228" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="5">
         <v>39</v>
       </c>
@@ -5018,7 +5961,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="229" spans="1:6" customHeight="1" ht="18.6">
+    <row r="229" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="5">
         <v>40</v>
       </c>
@@ -5035,7 +5978,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="230" spans="1:6" customHeight="1" ht="18.6">
+    <row r="230" spans="1:5" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="5">
         <v>41</v>
       </c>
@@ -5052,7 +5995,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="231" spans="1:6" customHeight="1" ht="18.6">
+    <row r="231" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5">
         <v>42</v>
       </c>
@@ -5069,27 +6012,5021 @@
         <v>58</v>
       </c>
     </row>
-    <row r="232" spans="1:6" customHeight="1">
-      <c r="A232" s="4">
+    <row r="232" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="9">
         <v>1</v>
       </c>
-      <c r="B232" s="4" t="s">
+      <c r="B232" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="C232" s="4" t="s">
+      <c r="C232" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D232" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E232" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="9">
+        <v>2</v>
+      </c>
+      <c r="B233" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C233" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D233" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E233" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="9">
+        <v>3</v>
+      </c>
+      <c r="B234" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C234" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D234" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="E234" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="9">
+        <v>4</v>
+      </c>
+      <c r="B235" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C235" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D235" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E235" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="9">
+        <v>5</v>
+      </c>
+      <c r="B236" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C236" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D236" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E236" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="9">
+        <v>6</v>
+      </c>
+      <c r="B237" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C237" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D237" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="E237" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="9">
+        <v>7</v>
+      </c>
+      <c r="B238" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C238" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D238" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E238" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="9">
+        <v>8</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C239" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D239" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E239" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="9">
+        <v>9</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C240" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D240" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E240" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="9">
+        <v>10</v>
+      </c>
+      <c r="B241" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C241" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D241" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="E241" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="9">
+        <v>11</v>
+      </c>
+      <c r="B242" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C242" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D242" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="E242" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="9">
+        <v>12</v>
+      </c>
+      <c r="B243" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C243" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D243" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="E243" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="9">
+        <v>13</v>
+      </c>
+      <c r="B244" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C244" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D244" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="E244" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="9">
+        <v>14</v>
+      </c>
+      <c r="B245" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C245" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D245" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E245" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="9">
+        <v>15</v>
+      </c>
+      <c r="B246" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C246" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D246" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E246" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="9">
+        <v>16</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C247" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D247" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="E247" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="9">
+        <v>17</v>
+      </c>
+      <c r="B248" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C248" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D248" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E248" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="9">
+        <v>18</v>
+      </c>
+      <c r="B249" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C249" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D249" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E249" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="9">
+        <v>19</v>
+      </c>
+      <c r="B250" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C250" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D250" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="E250" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="9">
+        <v>20</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C251" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E251" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="9">
+        <v>21</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C252" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="E252" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="9">
+        <v>22</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C253" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E253" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A254" s="9">
+        <v>23</v>
+      </c>
+      <c r="B254" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C254" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D254" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="E254" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A255" s="9">
+        <v>24</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C255" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="E255" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A256" s="9">
+        <v>25</v>
+      </c>
+      <c r="B256" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C256" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D256" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="E256" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A257" s="9">
+        <v>26</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C257" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="E257" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="9">
+        <v>27</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C258" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="E258" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="9">
+        <v>28</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C259" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E259" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="9">
+        <v>29</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C260" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="E260" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="9">
+        <v>30</v>
+      </c>
+      <c r="B261" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C261" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="E261" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="9">
+        <v>31</v>
+      </c>
+      <c r="B262" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C262" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="E262" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="9">
+        <v>32</v>
+      </c>
+      <c r="B263" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C263" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D263" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="E263" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A264" s="9">
+        <v>33</v>
+      </c>
+      <c r="B264" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C264" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="E264" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A265" s="9">
+        <v>34</v>
+      </c>
+      <c r="B265" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C265" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="E265" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A266" s="9">
+        <v>35</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C266" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="E266" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A267" s="9">
+        <v>36</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C267" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D232" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E232" s="4">
+      <c r="D267" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="E267" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="9">
+        <v>37</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C268" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="E268" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A269" s="9">
+        <v>38</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C269" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="E269" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A270" s="9">
+        <v>39</v>
+      </c>
+      <c r="B270" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C270" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D270" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E270" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="9">
+        <v>40</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C271" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="E271" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A272" s="9">
+        <v>41</v>
+      </c>
+      <c r="B272" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C272" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D272" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="E272" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A273" s="9">
+        <v>42</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C273" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="E273" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A274" s="9">
+        <v>43</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C274" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E274" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="9">
+        <v>44</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C275" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D275" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="E275" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="9">
+        <v>45</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C276" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D276" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E276" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="9">
+        <v>46</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C277" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D277" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="E277" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A278" s="9">
+        <v>47</v>
+      </c>
+      <c r="B278" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C278" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D278" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E278" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A279" s="9">
+        <v>48</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C279" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="E279" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A280" s="9">
+        <v>49</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C280" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D280" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="E280" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A281" s="9">
+        <v>50</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C281" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D281" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="E281" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A282" s="9">
+        <v>51</v>
+      </c>
+      <c r="B282" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C282" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D282" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E282" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A283" s="9">
+        <v>52</v>
+      </c>
+      <c r="B283" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C283" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D283" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="E283" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A284" s="9">
+        <v>53</v>
+      </c>
+      <c r="B284" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C284" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D284" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="E284" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A285" s="9">
+        <v>1</v>
+      </c>
+      <c r="B285" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C285" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D285" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E285" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A286" s="9">
+        <v>2</v>
+      </c>
+      <c r="B286" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C286" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="E286" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A287" s="9">
         <v>3</v>
       </c>
+      <c r="B287" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C287" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D287" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="E287" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A288" s="9">
+        <v>4</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C288" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E288" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A289" s="9">
+        <v>5</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C289" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D289" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="E289" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A290" s="9">
+        <v>6</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C290" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D290" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="E290" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A291" s="9">
+        <v>7</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C291" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="E291" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A292" s="9">
+        <v>8</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C292" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D292" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="E292" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A293" s="9">
+        <v>9</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C293" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D293" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E293" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A294" s="9">
+        <v>10</v>
+      </c>
+      <c r="B294" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C294" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D294" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="E294" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A295" s="9">
+        <v>11</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C295" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D295" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="E295" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A296" s="9">
+        <v>12</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C296" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D296" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="E296" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A297" s="9">
+        <v>13</v>
+      </c>
+      <c r="B297" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C297" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D297" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E297" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A298" s="9">
+        <v>14</v>
+      </c>
+      <c r="B298" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C298" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D298" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="E298" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A299" s="9">
+        <v>15</v>
+      </c>
+      <c r="B299" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C299" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D299" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E299" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="9">
+        <v>16</v>
+      </c>
+      <c r="B300" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C300" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D300" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="E300" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A301" s="9">
+        <v>17</v>
+      </c>
+      <c r="B301" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C301" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D301" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="E301" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A302" s="9">
+        <v>18</v>
+      </c>
+      <c r="B302" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C302" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D302" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E302" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A303" s="9">
+        <v>19</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C303" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D303" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="E303" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A304" s="9">
+        <v>20</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C304" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D304" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E304" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A305" s="9">
+        <v>21</v>
+      </c>
+      <c r="B305" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C305" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D305" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="E305" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A306" s="9">
+        <v>22</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C306" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D306" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E306" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A307" s="9">
+        <v>23</v>
+      </c>
+      <c r="B307" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C307" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D307" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E307" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A308" s="9">
+        <v>24</v>
+      </c>
+      <c r="B308" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C308" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D308" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E308" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="9">
+        <v>25</v>
+      </c>
+      <c r="B309" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C309" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D309" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="E309" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A310" s="9">
+        <v>26</v>
+      </c>
+      <c r="B310" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C310" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D310" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E310" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A311" s="9">
+        <v>27</v>
+      </c>
+      <c r="B311" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C311" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D311" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="E311" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A312" s="9">
+        <v>28</v>
+      </c>
+      <c r="B312" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C312" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D312" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E312" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A313" s="9">
+        <v>29</v>
+      </c>
+      <c r="B313" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C313" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D313" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="E313" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A314" s="9">
+        <v>30</v>
+      </c>
+      <c r="B314" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C314" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D314" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E314" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A315" s="9">
+        <v>31</v>
+      </c>
+      <c r="B315" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C315" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D315" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="E315" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A316" s="9">
+        <v>32</v>
+      </c>
+      <c r="B316" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C316" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D316" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="E316" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A317" s="9">
+        <v>33</v>
+      </c>
+      <c r="B317" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C317" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D317" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="E317" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A318" s="9">
+        <v>34</v>
+      </c>
+      <c r="B318" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C318" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D318" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E318" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A319" s="9">
+        <v>35</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C319" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D319" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="E319" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="9">
+        <v>36</v>
+      </c>
+      <c r="B320" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C320" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D320" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="E320" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="9">
+        <v>37</v>
+      </c>
+      <c r="B321" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C321" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D321" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="E321" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A322" s="9">
+        <v>38</v>
+      </c>
+      <c r="B322" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C322" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D322" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="E322" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A323" s="9">
+        <v>39</v>
+      </c>
+      <c r="B323" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C323" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D323" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="E323" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A324" s="9">
+        <v>40</v>
+      </c>
+      <c r="B324" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C324" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D324" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="E324" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A325" s="9">
+        <v>41</v>
+      </c>
+      <c r="B325" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C325" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D325" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="E325" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="9">
+        <v>42</v>
+      </c>
+      <c r="B326" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C326" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D326" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="E326" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="9">
+        <v>43</v>
+      </c>
+      <c r="B327" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C327" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D327" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="E327" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="9">
+        <v>44</v>
+      </c>
+      <c r="B328" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C328" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D328" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="E328" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="9">
+        <v>45</v>
+      </c>
+      <c r="B329" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C329" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D329" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="E329" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="9">
+        <v>46</v>
+      </c>
+      <c r="B330" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C330" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D330" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E330" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A331" s="9">
+        <v>47</v>
+      </c>
+      <c r="B331" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C331" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D331" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="E331" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A332" s="9">
+        <v>48</v>
+      </c>
+      <c r="B332" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C332" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D332" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="E332" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A333" s="9">
+        <v>49</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C333" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D333" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="E333" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="9">
+        <v>50</v>
+      </c>
+      <c r="B334" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C334" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D334" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="E334" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A335" s="9">
+        <v>51</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C335" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D335" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="E335" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A336" s="9">
+        <v>52</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C336" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D336" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="E336" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A337" s="9">
+        <v>53</v>
+      </c>
+      <c r="B337" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C337" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D337" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="E337" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A338" s="9">
+        <v>54</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C338" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D338" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="E338" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A339" s="9">
+        <v>1</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C339" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D339" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="E339" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A340" s="9">
+        <v>2</v>
+      </c>
+      <c r="B340" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C340" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D340" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="E340" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A341" s="9">
+        <v>3</v>
+      </c>
+      <c r="B341" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C341" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D341" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="E341" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A342" s="9">
+        <v>4</v>
+      </c>
+      <c r="B342" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C342" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D342" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="E342" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A343" s="9">
+        <v>5</v>
+      </c>
+      <c r="B343" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C343" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D343" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="E343" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A344" s="9">
+        <v>6</v>
+      </c>
+      <c r="B344" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C344" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D344" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="E344" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A345" s="9">
+        <v>7</v>
+      </c>
+      <c r="B345" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C345" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D345" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="E345" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A346" s="9">
+        <v>8</v>
+      </c>
+      <c r="B346" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C346" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D346" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="E346" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A347" s="9">
+        <v>9</v>
+      </c>
+      <c r="B347" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C347" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D347" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="E347" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A348" s="9">
+        <v>10</v>
+      </c>
+      <c r="B348" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C348" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D348" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="E348" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A349" s="9">
+        <v>11</v>
+      </c>
+      <c r="B349" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C349" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D349" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="E349" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A350" s="9">
+        <v>12</v>
+      </c>
+      <c r="B350" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C350" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D350" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="E350" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A351" s="9">
+        <v>13</v>
+      </c>
+      <c r="B351" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C351" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D351" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="E351" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A352" s="9">
+        <v>14</v>
+      </c>
+      <c r="B352" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C352" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D352" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="E352" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A353" s="9">
+        <v>15</v>
+      </c>
+      <c r="B353" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C353" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D353" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="E353" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A354" s="9">
+        <v>16</v>
+      </c>
+      <c r="B354" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C354" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D354" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="E354" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A355" s="9">
+        <v>17</v>
+      </c>
+      <c r="B355" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C355" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D355" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="E355" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A356" s="9">
+        <v>18</v>
+      </c>
+      <c r="B356" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C356" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D356" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="E356" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A357" s="9">
+        <v>19</v>
+      </c>
+      <c r="B357" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C357" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D357" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="E357" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A358" s="9">
+        <v>20</v>
+      </c>
+      <c r="B358" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C358" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D358" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="E358" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A359" s="9">
+        <v>21</v>
+      </c>
+      <c r="B359" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C359" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D359" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="E359" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A360" s="9">
+        <v>22</v>
+      </c>
+      <c r="B360" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C360" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D360" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="E360" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A361" s="9">
+        <v>23</v>
+      </c>
+      <c r="B361" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C361" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D361" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="E361" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A362" s="9">
+        <v>24</v>
+      </c>
+      <c r="B362" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C362" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D362" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="E362" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A363" s="9">
+        <v>25</v>
+      </c>
+      <c r="B363" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C363" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D363" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="E363" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="9">
+        <v>26</v>
+      </c>
+      <c r="B364" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C364" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D364" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="E364" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A365" s="9">
+        <v>27</v>
+      </c>
+      <c r="B365" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C365" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D365" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E365" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A366" s="9">
+        <v>28</v>
+      </c>
+      <c r="B366" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C366" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D366" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="E366" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A367" s="9">
+        <v>29</v>
+      </c>
+      <c r="B367" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C367" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D367" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="E367" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A368" s="9">
+        <v>30</v>
+      </c>
+      <c r="B368" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C368" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D368" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="E368" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A369" s="9">
+        <v>31</v>
+      </c>
+      <c r="B369" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C369" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D369" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="E369" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A370" s="9">
+        <v>32</v>
+      </c>
+      <c r="B370" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C370" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D370" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="E370" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A371" s="9">
+        <v>33</v>
+      </c>
+      <c r="B371" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C371" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D371" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="E371" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="9">
+        <v>34</v>
+      </c>
+      <c r="B372" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C372" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D372" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="E372" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A373" s="9">
+        <v>35</v>
+      </c>
+      <c r="B373" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C373" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D373" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="E373" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A374" s="9">
+        <v>36</v>
+      </c>
+      <c r="B374" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C374" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D374" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="E374" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A375" s="9">
+        <v>1</v>
+      </c>
+      <c r="B375" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C375" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D375" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="E375" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A376" s="9">
+        <v>2</v>
+      </c>
+      <c r="B376" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C376" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D376" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="E376" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="9">
+        <v>3</v>
+      </c>
+      <c r="B377" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C377" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D377" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="E377" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A378" s="9">
+        <v>4</v>
+      </c>
+      <c r="B378" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C378" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D378" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="E378" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A379" s="9">
+        <v>5</v>
+      </c>
+      <c r="B379" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C379" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D379" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="E379" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A380" s="9">
+        <v>6</v>
+      </c>
+      <c r="B380" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C380" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D380" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="E380" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A381" s="9">
+        <v>7</v>
+      </c>
+      <c r="B381" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C381" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D381" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="E381" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A382" s="9">
+        <v>8</v>
+      </c>
+      <c r="B382" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C382" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D382" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="E382" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A383" s="9">
+        <v>9</v>
+      </c>
+      <c r="B383" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C383" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D383" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="E383" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A384" s="9">
+        <v>10</v>
+      </c>
+      <c r="B384" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C384" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D384" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="E384" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A385" s="9">
+        <v>11</v>
+      </c>
+      <c r="B385" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C385" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D385" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="E385" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A386" s="9">
+        <v>12</v>
+      </c>
+      <c r="B386" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C386" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D386" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="E386" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A387" s="9">
+        <v>13</v>
+      </c>
+      <c r="B387" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C387" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D387" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="E387" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A388" s="9">
+        <v>14</v>
+      </c>
+      <c r="B388" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C388" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D388" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="E388" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A389" s="9">
+        <v>15</v>
+      </c>
+      <c r="B389" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C389" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D389" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="E389" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A390" s="9">
+        <v>16</v>
+      </c>
+      <c r="B390" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C390" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D390" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="E390" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A391" s="9">
+        <v>17</v>
+      </c>
+      <c r="B391" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C391" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D391" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="E391" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A392" s="9">
+        <v>18</v>
+      </c>
+      <c r="B392" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C392" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D392" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="E392" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A393" s="9">
+        <v>19</v>
+      </c>
+      <c r="B393" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C393" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D393" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E393" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A394" s="9">
+        <v>20</v>
+      </c>
+      <c r="B394" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C394" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D394" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="E394" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A395" s="9">
+        <v>21</v>
+      </c>
+      <c r="B395" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C395" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D395" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="E395" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A396" s="9">
+        <v>22</v>
+      </c>
+      <c r="B396" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C396" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D396" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="E396" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A397" s="9">
+        <v>23</v>
+      </c>
+      <c r="B397" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C397" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D397" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="E397" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A398" s="9">
+        <v>24</v>
+      </c>
+      <c r="B398" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C398" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D398" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="E398" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A399" s="9">
+        <v>25</v>
+      </c>
+      <c r="B399" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C399" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D399" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="E399" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A400" s="9">
+        <v>26</v>
+      </c>
+      <c r="B400" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C400" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D400" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="E400" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A401" s="9">
+        <v>27</v>
+      </c>
+      <c r="B401" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C401" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D401" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="E401" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A402" s="9">
+        <v>28</v>
+      </c>
+      <c r="B402" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C402" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D402" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="E402" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A403" s="9">
+        <v>29</v>
+      </c>
+      <c r="B403" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C403" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D403" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="E403" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A404" s="9">
+        <v>30</v>
+      </c>
+      <c r="B404" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C404" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D404" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="E404" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A405" s="9">
+        <v>31</v>
+      </c>
+      <c r="B405" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C405" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D405" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="E405" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A406" s="9">
+        <v>32</v>
+      </c>
+      <c r="B406" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C406" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D406" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="E406" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A407" s="9">
+        <v>33</v>
+      </c>
+      <c r="B407" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C407" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D407" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="E407" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A408" s="9">
+        <v>34</v>
+      </c>
+      <c r="B408" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C408" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D408" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="E408" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A409" s="9">
+        <v>35</v>
+      </c>
+      <c r="B409" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C409" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="D409" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="E409" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A410" s="9">
+        <v>36</v>
+      </c>
+      <c r="B410" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C410" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D410" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E410" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A411" s="9">
+        <v>37</v>
+      </c>
+      <c r="B411" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C411" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D411" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="E411" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A412" s="9">
+        <v>38</v>
+      </c>
+      <c r="B412" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C412" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D412" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="E412" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A413" s="9">
+        <v>39</v>
+      </c>
+      <c r="B413" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C413" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D413" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="E413" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A414" s="9">
+        <v>40</v>
+      </c>
+      <c r="B414" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C414" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D414" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="E414" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A415" s="9">
+        <v>41</v>
+      </c>
+      <c r="B415" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C415" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D415" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="E415" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A416" s="9">
+        <v>42</v>
+      </c>
+      <c r="B416" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C416" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D416" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="E416" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A417" s="9">
+        <v>43</v>
+      </c>
+      <c r="B417" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C417" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D417" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="E417" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A418" s="9">
+        <v>44</v>
+      </c>
+      <c r="B418" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C418" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D418" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="E418" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A419" s="9">
+        <v>45</v>
+      </c>
+      <c r="B419" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C419" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D419" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="E419" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A420" s="9">
+        <v>46</v>
+      </c>
+      <c r="B420" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C420" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="D420" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="E420" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A421" s="9">
+        <v>47</v>
+      </c>
+      <c r="B421" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C421" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D421" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="E421" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A422" s="9">
+        <v>48</v>
+      </c>
+      <c r="B422" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C422" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D422" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="E422" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A423" s="9">
+        <v>49</v>
+      </c>
+      <c r="B423" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C423" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D423" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="E423" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A424" s="9">
+        <v>50</v>
+      </c>
+      <c r="B424" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C424" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D424" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="E424" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A425" s="9">
+        <v>51</v>
+      </c>
+      <c r="B425" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C425" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D425" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="E425" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A426" s="9">
+        <v>52</v>
+      </c>
+      <c r="B426" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C426" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D426" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="E426" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A427" s="9">
+        <v>1</v>
+      </c>
+      <c r="B427" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C427" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D427" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="E427" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A428" s="9">
+        <v>2</v>
+      </c>
+      <c r="B428" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C428" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D428" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="E428" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A429" s="9">
+        <v>3</v>
+      </c>
+      <c r="B429" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C429" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D429" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="E429" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A430" s="9">
+        <v>4</v>
+      </c>
+      <c r="B430" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C430" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D430" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="E430" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A431" s="9">
+        <v>5</v>
+      </c>
+      <c r="B431" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C431" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D431" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="E431" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A432" s="9">
+        <v>6</v>
+      </c>
+      <c r="B432" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C432" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D432" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="E432" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A433" s="9">
+        <v>7</v>
+      </c>
+      <c r="B433" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C433" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D433" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="E433" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A434" s="9">
+        <v>8</v>
+      </c>
+      <c r="B434" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C434" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D434" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="E434" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A435" s="9">
+        <v>9</v>
+      </c>
+      <c r="B435" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C435" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D435" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="E435" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A436" s="9">
+        <v>10</v>
+      </c>
+      <c r="B436" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C436" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D436" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="E436" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A437" s="9">
+        <v>11</v>
+      </c>
+      <c r="B437" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C437" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D437" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="E437" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A438" s="9">
+        <v>12</v>
+      </c>
+      <c r="B438" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C438" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D438" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="E438" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A439" s="9">
+        <v>13</v>
+      </c>
+      <c r="B439" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C439" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D439" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="E439" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A440" s="9">
+        <v>14</v>
+      </c>
+      <c r="B440" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C440" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D440" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="E440" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A441" s="9">
+        <v>15</v>
+      </c>
+      <c r="B441" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C441" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D441" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="E441" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A442" s="9">
+        <v>16</v>
+      </c>
+      <c r="B442" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C442" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D442" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="E442" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A443" s="9">
+        <v>17</v>
+      </c>
+      <c r="B443" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C443" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D443" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="E443" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A444" s="9">
+        <v>18</v>
+      </c>
+      <c r="B444" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C444" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D444" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="E444" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A445" s="9">
+        <v>19</v>
+      </c>
+      <c r="B445" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C445" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D445" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E445" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A446" s="9">
+        <v>20</v>
+      </c>
+      <c r="B446" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C446" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D446" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="E446" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A447" s="9">
+        <v>21</v>
+      </c>
+      <c r="B447" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C447" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D447" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="E447" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A448" s="9">
+        <v>22</v>
+      </c>
+      <c r="B448" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C448" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D448" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="E448" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A449" s="9">
+        <v>23</v>
+      </c>
+      <c r="B449" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C449" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D449" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="E449" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A450" s="9">
+        <v>24</v>
+      </c>
+      <c r="B450" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C450" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D450" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="E450" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A451" s="9">
+        <v>25</v>
+      </c>
+      <c r="B451" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C451" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D451" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="E451" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A452" s="9">
+        <v>26</v>
+      </c>
+      <c r="B452" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C452" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D452" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="E452" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A453" s="9">
+        <v>27</v>
+      </c>
+      <c r="B453" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C453" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D453" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="E453" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A454" s="9">
+        <v>28</v>
+      </c>
+      <c r="B454" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C454" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D454" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="E454" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A455" s="9">
+        <v>29</v>
+      </c>
+      <c r="B455" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C455" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="D455" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="E455" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A456" s="9">
+        <v>30</v>
+      </c>
+      <c r="B456" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C456" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D456" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="E456" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A457" s="9">
+        <v>31</v>
+      </c>
+      <c r="B457" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C457" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D457" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="E457" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A458" s="9">
+        <v>32</v>
+      </c>
+      <c r="B458" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C458" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D458" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="E458" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A459" s="9">
+        <v>33</v>
+      </c>
+      <c r="B459" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C459" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D459" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="E459" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A460" s="9">
+        <v>34</v>
+      </c>
+      <c r="B460" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C460" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D460" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="E460" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A461" s="9">
+        <v>35</v>
+      </c>
+      <c r="B461" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C461" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D461" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="E461" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A462" s="9">
+        <v>36</v>
+      </c>
+      <c r="B462" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C462" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D462" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="E462" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A463" s="9">
+        <v>37</v>
+      </c>
+      <c r="B463" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C463" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D463" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="E463" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A464" s="9">
+        <v>38</v>
+      </c>
+      <c r="B464" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C464" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D464" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="E464" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A465" s="9">
+        <v>39</v>
+      </c>
+      <c r="B465" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C465" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D465" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="E465" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A466" s="9">
+        <v>40</v>
+      </c>
+      <c r="B466" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C466" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D466" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="E466" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A467" s="9">
+        <v>41</v>
+      </c>
+      <c r="B467" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C467" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D467" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="E467" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A468" s="9">
+        <v>42</v>
+      </c>
+      <c r="B468" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C468" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D468" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="E468" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A469" s="9">
+        <v>43</v>
+      </c>
+      <c r="B469" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C469" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="D469" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="E469" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A470" s="9">
+        <v>44</v>
+      </c>
+      <c r="B470" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C470" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D470" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="E470" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A471" s="9">
+        <v>45</v>
+      </c>
+      <c r="B471" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C471" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D471" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="E471" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A472" s="9">
+        <v>46</v>
+      </c>
+      <c r="B472" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C472" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D472" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="E472" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A473" s="9">
+        <v>47</v>
+      </c>
+      <c r="B473" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C473" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D473" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="E473" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A474" s="9">
+        <v>48</v>
+      </c>
+      <c r="B474" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C474" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D474" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="E474" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A475" s="9">
+        <v>49</v>
+      </c>
+      <c r="B475" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C475" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D475" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="E475" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A476" s="9">
+        <v>50</v>
+      </c>
+      <c r="B476" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C476" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D476" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="E476" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A477" s="9">
+        <v>51</v>
+      </c>
+      <c r="B477" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C477" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D477" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="E477" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A478" s="9">
+        <v>52</v>
+      </c>
+      <c r="B478" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C478" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D478" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="E478" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A479" s="9">
+        <v>1</v>
+      </c>
+      <c r="B479" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C479" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D479" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="E479" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A480" s="9">
+        <v>2</v>
+      </c>
+      <c r="B480" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C480" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D480" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E480" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A481" s="9">
+        <v>3</v>
+      </c>
+      <c r="B481" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C481" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D481" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="E481" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A482" s="9">
+        <v>4</v>
+      </c>
+      <c r="B482" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C482" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D482" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="E482" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A483" s="9">
+        <v>5</v>
+      </c>
+      <c r="B483" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C483" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D483" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="E483" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A484" s="9">
+        <v>6</v>
+      </c>
+      <c r="B484" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C484" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D484" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="E484" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A485" s="9">
+        <v>7</v>
+      </c>
+      <c r="B485" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C485" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D485" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="E485" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A486" s="9">
+        <v>8</v>
+      </c>
+      <c r="B486" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C486" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D486" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="E486" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A487" s="9">
+        <v>9</v>
+      </c>
+      <c r="B487" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C487" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D487" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="E487" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A488" s="9">
+        <v>10</v>
+      </c>
+      <c r="B488" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C488" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D488" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="E488" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A489" s="9">
+        <v>11</v>
+      </c>
+      <c r="B489" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C489" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D489" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="E489" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A490" s="9">
+        <v>12</v>
+      </c>
+      <c r="B490" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C490" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D490" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="E490" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A491" s="9">
+        <v>13</v>
+      </c>
+      <c r="B491" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C491" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D491" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="E491" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A492" s="9">
+        <v>14</v>
+      </c>
+      <c r="B492" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C492" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D492" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="E492" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A493" s="9">
+        <v>15</v>
+      </c>
+      <c r="B493" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C493" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D493" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="E493" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A494" s="9">
+        <v>16</v>
+      </c>
+      <c r="B494" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C494" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D494" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="E494" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A495" s="9">
+        <v>17</v>
+      </c>
+      <c r="B495" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C495" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D495" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="E495" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A496" s="9">
+        <v>18</v>
+      </c>
+      <c r="B496" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C496" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D496" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="E496" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A497" s="9">
+        <v>19</v>
+      </c>
+      <c r="B497" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C497" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D497" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="E497" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A498" s="9">
+        <v>20</v>
+      </c>
+      <c r="B498" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C498" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D498" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="E498" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A499" s="9">
+        <v>21</v>
+      </c>
+      <c r="B499" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C499" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D499" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="E499" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A500" s="9">
+        <v>22</v>
+      </c>
+      <c r="B500" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C500" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D500" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="E500" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A501" s="9">
+        <v>23</v>
+      </c>
+      <c r="B501" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C501" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D501" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="E501" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A502" s="9">
+        <v>24</v>
+      </c>
+      <c r="B502" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C502" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D502" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="E502" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A503" s="9">
+        <v>25</v>
+      </c>
+      <c r="B503" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C503" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D503" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="E503" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A504" s="9">
+        <v>26</v>
+      </c>
+      <c r="B504" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C504" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D504" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="E504" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A505" s="9">
+        <v>27</v>
+      </c>
+      <c r="B505" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C505" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D505" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="E505" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A506" s="9">
+        <v>28</v>
+      </c>
+      <c r="B506" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C506" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D506" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="E506" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A507" s="9">
+        <v>29</v>
+      </c>
+      <c r="B507" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C507" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D507" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="E507" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A508" s="9">
+        <v>30</v>
+      </c>
+      <c r="B508" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C508" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D508" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="E508" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="9">
+        <v>31</v>
+      </c>
+      <c r="B509" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C509" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D509" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="E509" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A510" s="9">
+        <v>32</v>
+      </c>
+      <c r="B510" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C510" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D510" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="E510" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A511" s="9">
+        <v>33</v>
+      </c>
+      <c r="B511" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C511" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D511" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="E511" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A512" s="9">
+        <v>34</v>
+      </c>
+      <c r="B512" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C512" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D512" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="E512" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A513" s="9">
+        <v>35</v>
+      </c>
+      <c r="B513" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C513" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D513" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="E513" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A514" s="9">
+        <v>36</v>
+      </c>
+      <c r="B514" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C514" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D514" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="E514" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A515" s="9">
+        <v>37</v>
+      </c>
+      <c r="B515" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C515" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D515" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E515" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A516" s="9">
+        <v>38</v>
+      </c>
+      <c r="B516" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C516" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D516" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="E516" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A517" s="9">
+        <v>39</v>
+      </c>
+      <c r="B517" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C517" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D517" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="E517" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A518" s="9">
+        <v>40</v>
+      </c>
+      <c r="B518" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C518" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D518" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="E518" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A519" s="9">
+        <v>42</v>
+      </c>
+      <c r="B519" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C519" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D519" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E519" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A520" s="9">
+        <v>43</v>
+      </c>
+      <c r="B520" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C520" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D520" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="E520" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A521" s="9">
+        <v>44</v>
+      </c>
+      <c r="B521" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C521" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="D521" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="E521" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A522" s="9">
+        <v>45</v>
+      </c>
+      <c r="B522" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C522" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D522" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="E522" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A523" s="9">
+        <v>46</v>
+      </c>
+      <c r="B523" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C523" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D523" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="E523" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A524" s="9">
+        <v>47</v>
+      </c>
+      <c r="B524" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C524" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D524" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="E524" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A525" s="9">
+        <v>48</v>
+      </c>
+      <c r="B525" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C525" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D525" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="E525" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A526" s="9">
+        <v>49</v>
+      </c>
+      <c r="B526" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C526" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D526" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="E526" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E231"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <autoFilter ref="A1:E231" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>